--- a/china.xlsx
+++ b/china.xlsx
@@ -16,39 +16,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="25">
   <si>
     <t>Track</t>
   </si>
   <si>
-    <t>JT5470775334324</t>
-  </si>
-  <si>
-    <t>YT8854351456860</t>
-  </si>
-  <si>
-    <t>JT5470865551856</t>
-  </si>
-  <si>
-    <t>JT5470609012999</t>
-  </si>
-  <si>
-    <t>JT5470913462897</t>
-  </si>
-  <si>
-    <t>YT8854242604846</t>
-  </si>
-  <si>
-    <t>JT5470986842366</t>
-  </si>
-  <si>
-    <t>JT9000379440120</t>
-  </si>
-  <si>
-    <t>JT5470675197035</t>
-  </si>
-  <si>
-    <t>YT8854147994079</t>
+    <t>YT8878256195196</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>Yusuf 501250707</t>
+  </si>
+  <si>
+    <t>YT8878190975603</t>
+  </si>
+  <si>
+    <t>Fayyoz0888-927080406</t>
+  </si>
+  <si>
+    <t>JT5495806308084</t>
+  </si>
+  <si>
+    <t>JT5495899178526</t>
+  </si>
+  <si>
+    <t>Anvar 977205225</t>
+  </si>
+  <si>
+    <t>Alisher0004-777016333</t>
+  </si>
+  <si>
+    <t>JT5496380854606</t>
+  </si>
+  <si>
+    <t>JT5495433647705</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>16.06.2026</t>
+  </si>
+  <si>
+    <t>JT5495342616032</t>
+  </si>
+  <si>
+    <t>JT5496389040454</t>
+  </si>
+  <si>
+    <t>JT5496376872907</t>
+  </si>
+  <si>
+    <t>JT5495394393083</t>
+  </si>
+  <si>
+    <t>JT5496270516915</t>
+  </si>
+  <si>
+    <t>JT5496376810838</t>
+  </si>
+  <si>
+    <t>YT8877267471668</t>
+  </si>
+  <si>
+    <t>JT5495399331306</t>
+  </si>
+  <si>
+    <t>YT8877225732475</t>
+  </si>
+  <si>
+    <t>JT5496392281486</t>
+  </si>
+  <si>
+    <t>JT5496410411821</t>
   </si>
 </sst>
 </file>
@@ -390,210 +432,672 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="1" max="1" width="29.21875" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>777395699521352</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>465213674738315</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>79114287730818</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>79113721261163</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>465213746448369</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+        <v>79114199400506</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>777395904669571</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+        <v>79114203887940</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>777395370783202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+        <v>777418407164674</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>79114287731046</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>78590880454846</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+        <v>79114114585570</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>9815123071354</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+        <v>9817311547938</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>9815131732878</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+        <v>777418210107128</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>777418540098081</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>79114008929258</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>79114123496019</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>79011910916564</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>435105216433867</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>777395904939220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>465213673466968</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>777395310545890</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>465214392736632</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>312973436038843</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>79114056552890</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>465211380153889</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>465214379765223</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>777395385320132</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+        <v>79011810156917</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>79114129226699</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>78590982581434</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+        <v>79114119950813</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>78591147514001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>78992151921056</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+        <v>79113831226396</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>79114249344806</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>9817286636034</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>9817306833974</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>9817266811309</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>79114119952579</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>79113859937536</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>9817310662063</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>79113826114819</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>79114123512156</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>9817293577073</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>79114123473093</v>
+      </c>
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>79114114546115</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>465426010024137</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>9817293845966</v>
+      </c>
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>79114224672451</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>9817310661010</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>79114096392960</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>777417680528740</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>465212009576148</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>78590960122866</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <v>777395926703260</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>79114114545731</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>79114123470502</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>79114158480850</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>79114287730634</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>79011815866016</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>777418512271860</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
-        <v>78590774805373</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
-        <v>9815070793492</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
-        <v>465206778108591</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
-        <v>465212755781706</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
-        <v>777395658338318</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
-        <v>78590911113245</v>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,81 +16,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="33">
   <si>
     <t>Track</t>
   </si>
   <si>
-    <t>YT8878256195196</t>
-  </si>
-  <si>
     <t>NAME</t>
   </si>
   <si>
     <t>Yusuf 501250707</t>
   </si>
   <si>
-    <t>YT8878190975603</t>
-  </si>
-  <si>
-    <t>Fayyoz0888-927080406</t>
-  </si>
-  <si>
-    <t>JT5495806308084</t>
-  </si>
-  <si>
-    <t>JT5495899178526</t>
-  </si>
-  <si>
     <t>Anvar 977205225</t>
   </si>
   <si>
     <t>Alisher0004-777016333</t>
   </si>
   <si>
-    <t>JT5496380854606</t>
-  </si>
-  <si>
-    <t>JT5495433647705</t>
-  </si>
-  <si>
     <t>DATE</t>
   </si>
   <si>
-    <t>16.06.2026</t>
-  </si>
-  <si>
-    <t>JT5495342616032</t>
-  </si>
-  <si>
-    <t>JT5496389040454</t>
-  </si>
-  <si>
-    <t>JT5496376872907</t>
-  </si>
-  <si>
-    <t>JT5495394393083</t>
-  </si>
-  <si>
-    <t>JT5496270516915</t>
-  </si>
-  <si>
-    <t>JT5496376810838</t>
-  </si>
-  <si>
-    <t>YT8877267471668</t>
-  </si>
-  <si>
-    <t>JT5495399331306</t>
-  </si>
-  <si>
-    <t>YT8877225732475</t>
-  </si>
-  <si>
-    <t>JT5496392281486</t>
-  </si>
-  <si>
-    <t>JT5496410411821</t>
+    <t>Hilola 555572809</t>
+  </si>
+  <si>
+    <t>JT5496397081847</t>
+  </si>
+  <si>
+    <t>YT8878373344697</t>
+  </si>
+  <si>
+    <t>YT8878433846646</t>
+  </si>
+  <si>
+    <t>YT8878364185573</t>
+  </si>
+  <si>
+    <t>YT8878891266189</t>
+  </si>
+  <si>
+    <t>BAHTIGUL 875266000</t>
+  </si>
+  <si>
+    <t>Islombek 783349009</t>
+  </si>
+  <si>
+    <t>YT8878013142445</t>
+  </si>
+  <si>
+    <t>JT5496426439535</t>
+  </si>
+  <si>
+    <t>YT8878973794278</t>
+  </si>
+  <si>
+    <t>YT8878892869002</t>
+  </si>
+  <si>
+    <t>YT8877957922382</t>
+  </si>
+  <si>
+    <t>Hasanjon 9283135944</t>
+  </si>
+  <si>
+    <t>JT5496532028174</t>
+  </si>
+  <si>
+    <t>JT5496397100619</t>
+  </si>
+  <si>
+    <t>YT8877954257843</t>
+  </si>
+  <si>
+    <t>YT8878924839212</t>
+  </si>
+  <si>
+    <t>YT8878489431799</t>
+  </si>
+  <si>
+    <t>JT5496555809498</t>
+  </si>
+  <si>
+    <t>JT5496083260646</t>
+  </si>
+  <si>
+    <t>YT8877978258660</t>
+  </si>
+  <si>
+    <t>JT5496426856472</t>
+  </si>
+  <si>
+    <t>JT5495975576123</t>
+  </si>
+  <si>
+    <t>JT5496562912088</t>
+  </si>
+  <si>
+    <t>YT8878376042259</t>
+  </si>
+  <si>
+    <t>YT8877953717504</t>
   </si>
 </sst>
 </file>
@@ -126,10 +150,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -432,405 +459,300 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.21875" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" customWidth="1"/>
-    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="4" max="4" width="23.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
+      <c r="A2" s="1">
+        <v>79114218356055</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
+      <c r="A3" s="1">
+        <v>79012581856167</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>79114287730818</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
+        <v>79114409063138</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>79113721261163</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
+        <v>79114218396909</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>79114199400506</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
+        <v>9817337232960</v>
       </c>
       <c r="D6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
+      <c r="A7" s="1">
+        <v>465426605460787</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>79114203887940</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
+      <c r="A8" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>777418407164674</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
+        <v>79114347075820</v>
       </c>
       <c r="D9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>79114287731046</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
+      <c r="A10" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>79114114585570</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
+      <c r="A11" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>9817311547938</v>
-      </c>
-      <c r="C12" t="s">
-        <v>13</v>
+      <c r="A12" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>777418210107128</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
+        <v>79114641590826</v>
       </c>
       <c r="D13" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>777418540098081</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
+      <c r="A15" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>79114008929258</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
+      <c r="A16" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>79114123496019</v>
-      </c>
-      <c r="C17" t="s">
-        <v>13</v>
+        <v>777419080528783</v>
       </c>
       <c r="D17" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>79011910916564</v>
-      </c>
-      <c r="C18" t="s">
-        <v>13</v>
+      <c r="A18" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>79114056552890</v>
-      </c>
-      <c r="C20" t="s">
-        <v>13</v>
+      <c r="A20" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" t="s">
-        <v>13</v>
+      <c r="A21" s="1">
+        <v>9817298550257</v>
       </c>
       <c r="D21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>79011810156917</v>
-      </c>
-      <c r="C22" t="s">
-        <v>13</v>
+        <v>9817338834087</v>
       </c>
       <c r="D22" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" t="s">
-        <v>13</v>
+      <c r="A23" s="1">
+        <v>79114351420184</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>79114129226699</v>
-      </c>
-      <c r="C24" t="s">
-        <v>13</v>
+        <v>79114523941757</v>
       </c>
       <c r="D24" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>79114119950813</v>
-      </c>
-      <c r="C26" t="s">
-        <v>13</v>
+      <c r="A26" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>79113831226396</v>
-      </c>
-      <c r="C27" t="s">
-        <v>13</v>
+      <c r="A27" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>79114249344806</v>
-      </c>
-      <c r="C29" t="s">
-        <v>13</v>
+      <c r="A29" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>9817286636034</v>
-      </c>
-      <c r="C30" t="s">
-        <v>13</v>
+        <v>465425273153619</v>
       </c>
       <c r="D30" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>9817306833974</v>
-      </c>
-      <c r="C32" t="s">
-        <v>13</v>
+        <v>79114272667800</v>
       </c>
       <c r="D32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" t="s">
-        <v>13</v>
+      <c r="A33" s="1">
+        <v>79114445687079</v>
       </c>
       <c r="D33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>9817266811309</v>
-      </c>
-      <c r="C34" t="s">
-        <v>13</v>
+        <v>777419340694859</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
-        <v>79114119952579</v>
-      </c>
-      <c r="C35" t="s">
-        <v>13</v>
+      <c r="A35" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" t="s">
-        <v>13</v>
+      <c r="A36" s="1">
+        <v>777419197107227</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
@@ -838,270 +760,95 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>79113859937536</v>
-      </c>
-      <c r="C37" t="s">
-        <v>13</v>
+        <v>777419193134582</v>
       </c>
       <c r="D37" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>9817310662063</v>
-      </c>
-      <c r="C38" t="s">
-        <v>13</v>
+        <v>777419149591288</v>
       </c>
       <c r="D38" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
-        <v>79113826114819</v>
-      </c>
-      <c r="C39" t="s">
-        <v>13</v>
+      <c r="A39" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>79114123512156</v>
-      </c>
-      <c r="C40" t="s">
-        <v>13</v>
+        <v>465427544369324</v>
       </c>
       <c r="D40" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
-        <v>9817293577073</v>
-      </c>
-      <c r="C41" t="s">
-        <v>13</v>
+      <c r="A41" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
-        <v>79114123473093</v>
-      </c>
-      <c r="C42" t="s">
-        <v>13</v>
+      <c r="A42" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D42" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" t="s">
-        <v>13</v>
+      <c r="A43" s="1">
+        <v>435227038851000</v>
       </c>
       <c r="D43" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
-        <v>79114114546115</v>
-      </c>
-      <c r="C44" t="s">
-        <v>13</v>
+      <c r="A44" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
-        <v>465426010024137</v>
-      </c>
-      <c r="C45" t="s">
-        <v>13</v>
+      <c r="A45" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
-        <v>9817293845966</v>
-      </c>
-      <c r="C46" t="s">
-        <v>13</v>
+      <c r="A46" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" t="s">
-        <v>13</v>
+      <c r="A47" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
-        <v>79114224672451</v>
-      </c>
-      <c r="C48" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
-        <v>9817310661010</v>
-      </c>
-      <c r="C49" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
-        <v>79114096392960</v>
-      </c>
-      <c r="C52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
-        <v>777417680528740</v>
-      </c>
-      <c r="C53" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
-        <v>79114114545731</v>
-      </c>
-      <c r="C54" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
-        <v>79114123470502</v>
-      </c>
-      <c r="C55" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
-        <v>79114158480850</v>
-      </c>
-      <c r="C56" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
-        <v>79114287730634</v>
-      </c>
-      <c r="C57" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
-        <v>79011815866016</v>
-      </c>
-      <c r="C58" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
-        <v>777418512271860</v>
-      </c>
-      <c r="C59" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>Track</t>
   </si>
@@ -265,6 +265,12 @@
   </si>
   <si>
     <t>79115778829822</t>
+  </si>
+  <si>
+    <t>77420713856011</t>
+  </si>
+  <si>
+    <t>465431595916185</t>
   </si>
 </sst>
 </file>
@@ -325,7 +331,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -335,6 +341,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -851,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -871,8 +880,8 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2">
-        <v>77420713856011</v>
+      <c r="A2" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1273,6 +1282,11 @@
     <row r="82" spans="1:1">
       <c r="A82" s="2" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>Track</t>
   </si>
@@ -271,6 +271,150 @@
   </si>
   <si>
     <t>465431595916185</t>
+  </si>
+  <si>
+    <t>777420362773842</t>
+  </si>
+  <si>
+    <t>773428109156580</t>
+  </si>
+  <si>
+    <t>465443036459439</t>
+  </si>
+  <si>
+    <t>JT5498684503822</t>
+  </si>
+  <si>
+    <t>777421096212600</t>
+  </si>
+  <si>
+    <t>YT8879913736413</t>
+  </si>
+  <si>
+    <t>YT8880510987456</t>
+  </si>
+  <si>
+    <t>777421365892035</t>
+  </si>
+  <si>
+    <t>465447506810494</t>
+  </si>
+  <si>
+    <t>9817528972077</t>
+  </si>
+  <si>
+    <t>JT9001972082680</t>
+  </si>
+  <si>
+    <t>JT5498569535322</t>
+  </si>
+  <si>
+    <t>JT5498880650303</t>
+  </si>
+  <si>
+    <t>465447154216665</t>
+  </si>
+  <si>
+    <t>YT7628954567668</t>
+  </si>
+  <si>
+    <t>777421232224929</t>
+  </si>
+  <si>
+    <t>79116252056460</t>
+  </si>
+  <si>
+    <t>9817508074958</t>
+  </si>
+  <si>
+    <t>9817450914859</t>
+  </si>
+  <si>
+    <t>YT8879882443578</t>
+  </si>
+  <si>
+    <t>465448988108738</t>
+  </si>
+  <si>
+    <t>465444445672611</t>
+  </si>
+  <si>
+    <t>777421365313677</t>
+  </si>
+  <si>
+    <t>777421046930615</t>
+  </si>
+  <si>
+    <t>79013823518038</t>
+  </si>
+  <si>
+    <t>YT8879925973530</t>
+  </si>
+  <si>
+    <t>JT5498044681933</t>
+  </si>
+  <si>
+    <t>JT5498262384603</t>
+  </si>
+  <si>
+    <t>777420364234201</t>
+  </si>
+  <si>
+    <t>9817512182414</t>
+  </si>
+  <si>
+    <t>YT8880292978538</t>
+  </si>
+  <si>
+    <t>JT5498130519084</t>
+  </si>
+  <si>
+    <t>9817479807223</t>
+  </si>
+  <si>
+    <t>777420107395099</t>
+  </si>
+  <si>
+    <t>9817494430164</t>
+  </si>
+  <si>
+    <t>777420209995112</t>
+  </si>
+  <si>
+    <t>9817475375924</t>
+  </si>
+  <si>
+    <t>79116064173156</t>
+  </si>
+  <si>
+    <t>465445620423811</t>
+  </si>
+  <si>
+    <t>79115916921709</t>
+  </si>
+  <si>
+    <t>465445838248752</t>
+  </si>
+  <si>
+    <t>9817455768664</t>
+  </si>
+  <si>
+    <t>777420415699128</t>
+  </si>
+  <si>
+    <t>JT5498515169938</t>
+  </si>
+  <si>
+    <t>777420320755106</t>
+  </si>
+  <si>
+    <t>_x000D_777420148088605</t>
+  </si>
+  <si>
+    <t>777420190077415</t>
+  </si>
+  <si>
+    <t>777421190698415</t>
   </si>
 </sst>
 </file>
@@ -331,7 +475,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -344,6 +488,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -860,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -1287,6 +1440,246 @@
     <row r="83" spans="1:1">
       <c r="A83" s="4" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="7" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>Track</t>
   </si>
@@ -25,6 +25,249 @@
   </si>
   <si>
     <t>DATE</t>
+  </si>
+  <si>
+    <t>YT8880982299813</t>
+  </si>
+  <si>
+    <t>JT5498633122296</t>
+  </si>
+  <si>
+    <t>9817598337810</t>
+  </si>
+  <si>
+    <t>9817561906196</t>
+  </si>
+  <si>
+    <t>9817597042198</t>
+  </si>
+  <si>
+    <t>79116860524513</t>
+  </si>
+  <si>
+    <t>465453312175650</t>
+  </si>
+  <si>
+    <t>YT8881001428247</t>
+  </si>
+  <si>
+    <t>79117054093610</t>
+  </si>
+  <si>
+    <t>79116352158884</t>
+  </si>
+  <si>
+    <t>465455321353258</t>
+  </si>
+  <si>
+    <t>JT5499824273016</t>
+  </si>
+  <si>
+    <t>465448606440063</t>
+  </si>
+  <si>
+    <t>YT8881014957527</t>
+  </si>
+  <si>
+    <t>JT5499254571451</t>
+  </si>
+  <si>
+    <t>777420974852832</t>
+  </si>
+  <si>
+    <t>777421102032945</t>
+  </si>
+  <si>
+    <t>465453390178582</t>
+  </si>
+  <si>
+    <t>YT8881016845806</t>
+  </si>
+  <si>
+    <t>JT5499581951689</t>
+  </si>
+  <si>
+    <t>777422365205500</t>
+  </si>
+  <si>
+    <t>9817590201640</t>
+  </si>
+  <si>
+    <t>9817585314171</t>
+  </si>
+  <si>
+    <t>777422086167392</t>
+  </si>
+  <si>
+    <t>777422047937564</t>
+  </si>
+  <si>
+    <t>JT5499420492228</t>
+  </si>
+  <si>
+    <t>465456795812468</t>
+  </si>
+  <si>
+    <t>777421947371815</t>
+  </si>
+  <si>
+    <t>777422098989110</t>
+  </si>
+  <si>
+    <t>79117395794341</t>
+  </si>
+  <si>
+    <t>777422249209050</t>
+  </si>
+  <si>
+    <t>JT5499557335871</t>
+  </si>
+  <si>
+    <t>JT5499593076310</t>
+  </si>
+  <si>
+    <t>9817601310341</t>
+  </si>
+  <si>
+    <t>JT5499459270971</t>
+  </si>
+  <si>
+    <t>777421979396975</t>
+  </si>
+  <si>
+    <t>465451760956911</t>
+  </si>
+  <si>
+    <t>9817587706895</t>
+  </si>
+  <si>
+    <t>8258794480420</t>
+  </si>
+  <si>
+    <t>465454450241432</t>
+  </si>
+  <si>
+    <t>YT8881827269921</t>
+  </si>
+  <si>
+    <t>465457764900348</t>
+  </si>
+  <si>
+    <t>9817599918493</t>
+  </si>
+  <si>
+    <t>79117436311943</t>
+  </si>
+  <si>
+    <t>777422232180626</t>
+  </si>
+  <si>
+    <t>465459292330949</t>
+  </si>
+  <si>
+    <t>9817587676356</t>
+  </si>
+  <si>
+    <t>79117070893183</t>
+  </si>
+  <si>
+    <t>79014648854833</t>
+  </si>
+  <si>
+    <t>YT8881264556325</t>
+  </si>
+  <si>
+    <t>9817611933106</t>
+  </si>
+  <si>
+    <t>JT5499474471835</t>
+  </si>
+  <si>
+    <t>YT8881205713280</t>
+  </si>
+  <si>
+    <t>YT8881713805039</t>
+  </si>
+  <si>
+    <t>777422057138983</t>
+  </si>
+  <si>
+    <t>777422279578535</t>
+  </si>
+  <si>
+    <t>JT5499357097713</t>
+  </si>
+  <si>
+    <t>9817583571857</t>
+  </si>
+  <si>
+    <t>465459149313511</t>
+  </si>
+  <si>
+    <t>435243081637711</t>
+  </si>
+  <si>
+    <t>YT8881203079304</t>
+  </si>
+  <si>
+    <t>YT8881710489346</t>
+  </si>
+  <si>
+    <t>JT5499555318372</t>
+  </si>
+  <si>
+    <t>777422224291867</t>
+  </si>
+  <si>
+    <t>777421855554896</t>
+  </si>
+  <si>
+    <t>79117774445858</t>
+  </si>
+  <si>
+    <t>9817607428330</t>
+  </si>
+  <si>
+    <t>465450172258904</t>
+  </si>
+  <si>
+    <t>777421939569475</t>
+  </si>
+  <si>
+    <t>YT8881256136317</t>
+  </si>
+  <si>
+    <t>JT5499708160992</t>
+  </si>
+  <si>
+    <t>79117415228084</t>
+  </si>
+  <si>
+    <t>9817606613366</t>
+  </si>
+  <si>
+    <t>79117509710669</t>
+  </si>
+  <si>
+    <t>9817577879969</t>
+  </si>
+  <si>
+    <t>JT5499505166782</t>
+  </si>
+  <si>
+    <t>777421616975217</t>
+  </si>
+  <si>
+    <t>79117696250946</t>
+  </si>
+  <si>
+    <t>79117465527523</t>
+  </si>
+  <si>
+    <t>9817572476799</t>
+  </si>
+  <si>
+    <t>777422227310805</t>
   </si>
 </sst>
 </file>
@@ -55,12 +298,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -70,10 +328,22 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -590,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -607,6 +877,411 @@
       </c>
       <c r="D1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Track</t>
   </si>
@@ -25,6 +25,108 @@
   </si>
   <si>
     <t>DATE</t>
+  </si>
+  <si>
+    <t>YT8881595284182</t>
+  </si>
+  <si>
+    <t>YT8882260952847</t>
+  </si>
+  <si>
+    <t>YT8882494776859</t>
+  </si>
+  <si>
+    <t>YT8881755208728</t>
+  </si>
+  <si>
+    <t>YT8881657240525</t>
+  </si>
+  <si>
+    <t>YT8882144681960</t>
+  </si>
+  <si>
+    <t>JT5500131975712</t>
+  </si>
+  <si>
+    <t>YT8881755210383</t>
+  </si>
+  <si>
+    <t>YT8881755208849</t>
+  </si>
+  <si>
+    <t>YT8882396047152</t>
+  </si>
+  <si>
+    <t>JT5499595952076</t>
+  </si>
+  <si>
+    <t>YT8882309071744</t>
+  </si>
+  <si>
+    <t>JT5500220106336</t>
+  </si>
+  <si>
+    <t>YT8882440004894</t>
+  </si>
+  <si>
+    <t>JT5499973731091</t>
+  </si>
+  <si>
+    <t>JT5500042212292</t>
+  </si>
+  <si>
+    <t>JT5500386588411</t>
+  </si>
+  <si>
+    <t>JT5500705303808</t>
+  </si>
+  <si>
+    <t>YT8881664761417</t>
+  </si>
+  <si>
+    <t>YT8882023690124</t>
+  </si>
+  <si>
+    <t>YT8881965706708</t>
+  </si>
+  <si>
+    <t>YT8882049235336</t>
+  </si>
+  <si>
+    <t>JT5500085421454</t>
+  </si>
+  <si>
+    <t>YT8881981266714</t>
+  </si>
+  <si>
+    <t>YT8882084279009</t>
+  </si>
+  <si>
+    <t>JT5500709369606</t>
+  </si>
+  <si>
+    <t>YT8882331018326</t>
+  </si>
+  <si>
+    <t>YT8881923064217</t>
+  </si>
+  <si>
+    <t>JT5500171686135</t>
+  </si>
+  <si>
+    <t>JT5500642188425</t>
+  </si>
+  <si>
+    <t>YT8882082598760</t>
+  </si>
+  <si>
+    <t>YT8882105763850</t>
+  </si>
+  <si>
+    <t>SF5112110102446</t>
+  </si>
+  <si>
+    <t>YT8881876085352</t>
   </si>
 </sst>
 </file>
@@ -590,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -607,6 +709,466 @@
       </c>
       <c r="D1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1">
+        <v>777421971309997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1">
+        <v>79117952924235</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1">
+        <v>465458300612210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1">
+        <v>465462997566968</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1">
+        <v>9817637752976</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1">
+        <v>777422386231741</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1">
+        <v>777422549883964</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1">
+        <v>777422741197359</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1">
+        <v>79117641603383</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1">
+        <v>777422423684474</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1">
+        <v>79117947325687</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1">
+        <v>777422657466151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1">
+        <v>79118115286962</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1">
+        <v>465458348367580</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1">
+        <v>465464907314970</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1">
+        <v>777422134424763</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1">
+        <v>9817706152080</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1">
+        <v>9817641420345</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1">
+        <v>9817618218214</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1">
+        <v>777422513725104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1">
+        <v>79118024749653</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1">
+        <v>777422657905926</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1">
+        <v>777423203000463</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1">
+        <v>777422413035587</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1">
+        <v>79117818077517</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1">
+        <v>777422517419094</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1">
+        <v>9817699670146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1">
+        <v>9817626176674</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1">
+        <v>465464033007149</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1">
+        <v>9817684175880</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1">
+        <v>9817638532752</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1">
+        <v>79117975994426</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1">
+        <v>777422279037036</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1">
+        <v>465460191668107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1">
+        <v>465458538755029</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1">
+        <v>9817633727498</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1">
+        <v>79118367685893</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="1">
+        <v>9817700621226</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1">
+        <v>79117796071346</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1">
+        <v>465457962486311</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="1">
+        <v>777422731528745</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1">
+        <v>465462045052132</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="1">
+        <v>777422556482984</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="1">
+        <v>465464224986141</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="1">
+        <v>465461539296139</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="1">
+        <v>777422770801355</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="1">
+        <v>777423239248503</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="1">
+        <v>79117651536910</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="1">
+        <v>79117933681198</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="1">
+        <v>9817627085660</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="1">
+        <v>777422282995768</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="1">
+        <v>777423239698605</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="1">
+        <v>465465103750961</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="1">
+        <v>9817620085910</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="1">
+        <v>465457413048475</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="1">
+        <v>465456211470405</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="1">
+        <v>465464532957747</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="1">
+        <v>777423140486346</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
   <si>
     <t>Track</t>
   </si>
@@ -27,106 +27,229 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>YT8881595284182</t>
-  </si>
-  <si>
-    <t>YT8882260952847</t>
-  </si>
-  <si>
-    <t>YT8882494776859</t>
-  </si>
-  <si>
-    <t>YT8881755208728</t>
-  </si>
-  <si>
-    <t>YT8881657240525</t>
-  </si>
-  <si>
-    <t>YT8882144681960</t>
-  </si>
-  <si>
-    <t>JT5500131975712</t>
-  </si>
-  <si>
-    <t>YT8881755210383</t>
-  </si>
-  <si>
-    <t>YT8881755208849</t>
-  </si>
-  <si>
-    <t>YT8882396047152</t>
-  </si>
-  <si>
-    <t>JT5499595952076</t>
-  </si>
-  <si>
-    <t>YT8882309071744</t>
-  </si>
-  <si>
-    <t>JT5500220106336</t>
-  </si>
-  <si>
-    <t>YT8882440004894</t>
-  </si>
-  <si>
-    <t>JT5499973731091</t>
-  </si>
-  <si>
-    <t>JT5500042212292</t>
-  </si>
-  <si>
-    <t>JT5500386588411</t>
-  </si>
-  <si>
-    <t>JT5500705303808</t>
-  </si>
-  <si>
-    <t>YT8881664761417</t>
-  </si>
-  <si>
-    <t>YT8882023690124</t>
-  </si>
-  <si>
-    <t>YT8881965706708</t>
-  </si>
-  <si>
-    <t>YT8882049235336</t>
-  </si>
-  <si>
-    <t>JT5500085421454</t>
-  </si>
-  <si>
-    <t>YT8881981266714</t>
-  </si>
-  <si>
-    <t>YT8882084279009</t>
-  </si>
-  <si>
-    <t>JT5500709369606</t>
-  </si>
-  <si>
-    <t>YT8882331018326</t>
-  </si>
-  <si>
-    <t>YT8881923064217</t>
-  </si>
-  <si>
-    <t>JT5500171686135</t>
-  </si>
-  <si>
-    <t>JT5500642188425</t>
-  </si>
-  <si>
-    <t>YT8882082598760</t>
-  </si>
-  <si>
-    <t>YT8882105763850</t>
-  </si>
-  <si>
-    <t>SF5112110102446</t>
-  </si>
-  <si>
-    <t>YT8881876085352</t>
+    <t>79118257588609</t>
+  </si>
+  <si>
+    <t>YT888971825187</t>
+  </si>
+  <si>
+    <t>ＪＤＡＰ０３13258422</t>
+  </si>
+  <si>
+    <t>JDAP0313258422</t>
+  </si>
+  <si>
+    <t>79118367875866</t>
+  </si>
+  <si>
+    <t>777420282036519</t>
+  </si>
+  <si>
+    <t>79118276902896</t>
+  </si>
+  <si>
+    <t>79015519961480</t>
+  </si>
+  <si>
+    <t>79118373286841</t>
+  </si>
+  <si>
+    <t>JT550099745629</t>
+  </si>
+  <si>
+    <t>465474899950488</t>
+  </si>
+  <si>
+    <t>777422956038345</t>
+  </si>
+  <si>
+    <t>9817751764072</t>
+  </si>
+  <si>
+    <t>79118817209091</t>
+  </si>
+  <si>
+    <t>JT550478769131</t>
+  </si>
+  <si>
+    <t>79118138983288</t>
+  </si>
+  <si>
+    <t>ＹＴ８８８812345532</t>
+  </si>
+  <si>
+    <t>YT888812345532</t>
+  </si>
+  <si>
+    <t>79118656662606</t>
+  </si>
+  <si>
+    <t>777423388035728</t>
+  </si>
+  <si>
+    <t>ＹＴ８８８579129738</t>
+  </si>
+  <si>
+    <t>YT888579129738</t>
+  </si>
+  <si>
+    <t>9817758621431</t>
+  </si>
+  <si>
+    <t>YT8883068430782</t>
+  </si>
+  <si>
+    <t>YT888728725446</t>
+  </si>
+  <si>
+    <t>YT8882728725446</t>
+  </si>
+  <si>
+    <t>JT5500919745629</t>
+  </si>
+  <si>
+    <t>79015421313659</t>
+  </si>
+  <si>
+    <t>YT8883016778119</t>
+  </si>
+  <si>
+    <t>777422811535476</t>
+  </si>
+  <si>
+    <t>9817676881239</t>
+  </si>
+  <si>
+    <t>79118554290183</t>
+  </si>
+  <si>
+    <t>777423080271777</t>
+  </si>
+  <si>
+    <t>777422831741276</t>
+  </si>
+  <si>
+    <t>79118644923859</t>
+  </si>
+  <si>
+    <t>79118717367067</t>
+  </si>
+  <si>
+    <t>9817659220150</t>
+  </si>
+  <si>
+    <t>777423193264153</t>
+  </si>
+  <si>
+    <t>79118615476461</t>
+  </si>
+  <si>
+    <t>777423262190233</t>
+  </si>
+  <si>
+    <t>465463953627717</t>
+  </si>
+  <si>
+    <t>79118522980734</t>
+  </si>
+  <si>
+    <t>79118579258190</t>
+  </si>
+  <si>
+    <t>465459643712698</t>
+  </si>
+  <si>
+    <t>465466976923906</t>
+  </si>
+  <si>
+    <t>9817751470985</t>
+  </si>
+  <si>
+    <t>JT3168752156470</t>
+  </si>
+  <si>
+    <t>YT8881866116899</t>
+  </si>
+  <si>
+    <t>79118432746656</t>
+  </si>
+  <si>
+    <t>465468421375906</t>
+  </si>
+  <si>
+    <t>YT8883165794725</t>
+  </si>
+  <si>
+    <t>465467345765080</t>
+  </si>
+  <si>
+    <t>JT5500938255508</t>
+  </si>
+  <si>
+    <t>JT5500670686464</t>
+  </si>
+  <si>
+    <t>465475987318740</t>
+  </si>
+  <si>
+    <t>YT8881966666733</t>
+  </si>
+  <si>
+    <t>777422847337625</t>
+  </si>
+  <si>
+    <t>YT8882001189556</t>
+  </si>
+  <si>
+    <t>JT5500848779222</t>
+  </si>
+  <si>
+    <t>YT8882076042439</t>
+  </si>
+  <si>
+    <t>YT8881950927855</t>
+  </si>
+  <si>
+    <t>777423349497530</t>
+  </si>
+  <si>
+    <t>YT8882024475728</t>
+  </si>
+  <si>
+    <t>79118247028763</t>
+  </si>
+  <si>
+    <t>9817650895696</t>
+  </si>
+  <si>
+    <t>79118249168211</t>
+  </si>
+  <si>
+    <t>465466346707418</t>
+  </si>
+  <si>
+    <t>465467113069181</t>
+  </si>
+  <si>
+    <t>777423445904215</t>
+  </si>
+  <si>
+    <t>9817714904846</t>
+  </si>
+  <si>
+    <t>9817688850817</t>
+  </si>
+  <si>
+    <t>79118141365896</t>
+  </si>
+  <si>
+    <t>JT5501195769597</t>
+  </si>
+  <si>
+    <t>777423146909811</t>
+  </si>
+  <si>
+    <t>777423269005541</t>
   </si>
 </sst>
 </file>
@@ -157,12 +280,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -172,10 +310,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -692,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -712,463 +856,393 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1">
-        <v>777421971309997</v>
+      <c r="A2" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
+      <c r="A3" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
+      <c r="A4" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
+      <c r="A5" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
+      <c r="A6" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1">
-        <v>79117952924235</v>
+      <c r="A7" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1">
-        <v>465458300612210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1">
-        <v>465462997566968</v>
-      </c>
-    </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
+      <c r="A11" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1">
-        <v>9817637752976</v>
+      <c r="A12" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>9</v>
+      <c r="A13" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1">
-        <v>777422386231741</v>
+      <c r="A14" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>10</v>
+      <c r="A15" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
+      <c r="A16" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="1">
-        <v>777422549883964</v>
+      <c r="A17" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>12</v>
+      <c r="A18" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>13</v>
+      <c r="A19" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="1" t="s">
-        <v>14</v>
+      <c r="A20" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="1">
-        <v>777422741197359</v>
+      <c r="A21" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>15</v>
+      <c r="A22" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>16</v>
+      <c r="A23" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="1">
-        <v>79117641603383</v>
+      <c r="A24" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="1">
-        <v>777422423684474</v>
+      <c r="A25" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>17</v>
+      <c r="A26" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>18</v>
+      <c r="A27" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="1">
-        <v>79117947325687</v>
+      <c r="A28" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="1">
-        <v>777422657466151</v>
+      <c r="A29" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="1">
-        <v>79118115286962</v>
+      <c r="A30" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="1">
-        <v>465458348367580</v>
+      <c r="A31" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="1">
-        <v>465464907314970</v>
+      <c r="A32" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="1">
-        <v>777422134424763</v>
+      <c r="A33" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="1" t="s">
-        <v>19</v>
+      <c r="A34" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="1">
-        <v>9817706152080</v>
+      <c r="A35" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="1">
-        <v>9817641420345</v>
+      <c r="A36" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="1">
-        <v>9817618218214</v>
+      <c r="A37" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="1">
-        <v>777422513725104</v>
+      <c r="A38" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="1">
-        <v>79118024749653</v>
+      <c r="A39" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="1">
-        <v>777422657905926</v>
+      <c r="A40" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1">
-        <v>777423203000463</v>
+      <c r="A41" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="1">
-        <v>777422413035587</v>
+      <c r="A42" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="1">
-        <v>79117818077517</v>
+      <c r="A43" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="1">
-        <v>777422517419094</v>
+      <c r="A44" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="1">
-        <v>9817699670146</v>
+      <c r="A45" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="1">
-        <v>9817626176674</v>
+      <c r="A46" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>20</v>
+      <c r="A47" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>21</v>
+      <c r="A48" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="1">
-        <v>465464033007149</v>
+      <c r="A49" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="1">
-        <v>9817684175880</v>
+      <c r="A50" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="1">
-        <v>9817638532752</v>
+      <c r="A51" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="1">
-        <v>79117975994426</v>
+      <c r="A52" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="1">
-        <v>777422279037036</v>
+      <c r="A53" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="1">
-        <v>465460191668107</v>
+      <c r="A54" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="1">
-        <v>465458538755029</v>
+      <c r="A55" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="1">
-        <v>9817633727498</v>
+      <c r="A56" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="1" t="s">
-        <v>22</v>
+      <c r="A57" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>23</v>
+      <c r="A58" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="1" t="s">
-        <v>24</v>
+      <c r="A59" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="1" t="s">
-        <v>25</v>
+      <c r="A60" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="1">
-        <v>79118367685893</v>
+      <c r="A61" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="1" t="s">
-        <v>26</v>
+      <c r="A62" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="1">
-        <v>9817700621226</v>
+      <c r="A63" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="1">
-        <v>79117796071346</v>
+      <c r="A64" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="1">
-        <v>465457962486311</v>
+      <c r="A65" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>27</v>
+      <c r="A66" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="1">
-        <v>777422731528745</v>
+      <c r="A67" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>28</v>
+      <c r="A68" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="1">
-        <v>465462045052132</v>
+      <c r="A69" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="1" t="s">
-        <v>29</v>
+      <c r="A70" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="3" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="1">
-        <v>777422556482984</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="1">
-        <v>465464224986141</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="1">
-        <v>465461539296139</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="1">
-        <v>777422770801355</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="1">
-        <v>777423239248503</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="1">
-        <v>79117651536910</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="1">
-        <v>79117933681198</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="1">
-        <v>9817627085660</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="1">
-        <v>777422282995768</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="1">
-        <v>777423239698605</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="1">
-        <v>465465103750961</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="1">
-        <v>9817620085910</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="1">
-        <v>465457413048475</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="1">
-        <v>465456211470405</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="1">
-        <v>465464532957747</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="1">
-        <v>777423140486346</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="154">
   <si>
     <t>Track</t>
   </si>
@@ -250,6 +250,234 @@
   </si>
   <si>
     <t>777423269005541</t>
+  </si>
+  <si>
+    <t>JT5501371556169</t>
+  </si>
+  <si>
+    <t>YT8883049444988</t>
+  </si>
+  <si>
+    <t>YT8883182286722</t>
+  </si>
+  <si>
+    <t>YT8883723028714</t>
+  </si>
+  <si>
+    <t>YT8883849849679</t>
+  </si>
+  <si>
+    <t>JT5501535601748</t>
+  </si>
+  <si>
+    <t>YT8882874480068</t>
+  </si>
+  <si>
+    <t>JT5502597241614</t>
+  </si>
+  <si>
+    <t>JT5501299359983</t>
+  </si>
+  <si>
+    <t>YT8883626255907</t>
+  </si>
+  <si>
+    <t>YT8883742931987</t>
+  </si>
+  <si>
+    <t>YT8882892016005</t>
+  </si>
+  <si>
+    <t>JT5501077523127</t>
+  </si>
+  <si>
+    <t>YT8882970307102</t>
+  </si>
+  <si>
+    <t>JT5501302513659</t>
+  </si>
+  <si>
+    <t>YT8883239639732</t>
+  </si>
+  <si>
+    <t>YT8882580605650</t>
+  </si>
+  <si>
+    <t>YT8883674598074</t>
+  </si>
+  <si>
+    <t>JT5501532535801</t>
+  </si>
+  <si>
+    <t>JT5501532764591</t>
+  </si>
+  <si>
+    <t>JT5501372942277</t>
+  </si>
+  <si>
+    <t>YT8883410575516</t>
+  </si>
+  <si>
+    <t>YT8883595470376</t>
+  </si>
+  <si>
+    <t>79118824420191</t>
+  </si>
+  <si>
+    <t>465472981439634</t>
+  </si>
+  <si>
+    <t>777423766456070</t>
+  </si>
+  <si>
+    <t>777423791434285</t>
+  </si>
+  <si>
+    <t>465460557466698</t>
+  </si>
+  <si>
+    <t>79119115957783</t>
+  </si>
+  <si>
+    <t>465475730266001</t>
+  </si>
+  <si>
+    <t>79118908516350</t>
+  </si>
+  <si>
+    <t>79119040950183</t>
+  </si>
+  <si>
+    <t>79119327158321</t>
+  </si>
+  <si>
+    <t>9817718946799</t>
+  </si>
+  <si>
+    <t>79119089277103</t>
+  </si>
+  <si>
+    <t>9817751874305</t>
+  </si>
+  <si>
+    <t>79119471430708</t>
+  </si>
+  <si>
+    <t>79119050833173</t>
+  </si>
+  <si>
+    <t>9817605081138</t>
+  </si>
+  <si>
+    <t>9817784576370</t>
+  </si>
+  <si>
+    <t>9817753460786</t>
+  </si>
+  <si>
+    <t>9817769911867</t>
+  </si>
+  <si>
+    <t>79118833080186</t>
+  </si>
+  <si>
+    <t>79118979425089</t>
+  </si>
+  <si>
+    <t>777424572515165</t>
+  </si>
+  <si>
+    <t>9817653521677</t>
+  </si>
+  <si>
+    <t>777424114810896</t>
+  </si>
+  <si>
+    <t>79119137632359</t>
+  </si>
+  <si>
+    <t>465475448112441</t>
+  </si>
+  <si>
+    <t>9817780091264</t>
+  </si>
+  <si>
+    <t>79119299656526</t>
+  </si>
+  <si>
+    <t>777424092833669</t>
+  </si>
+  <si>
+    <t>777423532876975</t>
+  </si>
+  <si>
+    <t>465473412612728</t>
+  </si>
+  <si>
+    <t>777423875081346</t>
+  </si>
+  <si>
+    <t>777424007430464</t>
+  </si>
+  <si>
+    <t>777423571387306</t>
+  </si>
+  <si>
+    <t>9817736381529</t>
+  </si>
+  <si>
+    <t>777424099932425</t>
+  </si>
+  <si>
+    <t>777422837209675</t>
+  </si>
+  <si>
+    <t>465472312616126</t>
+  </si>
+  <si>
+    <t>465471732331470</t>
+  </si>
+  <si>
+    <t>465472002832188</t>
+  </si>
+  <si>
+    <t>777423767375582</t>
+  </si>
+  <si>
+    <t>777423745466795</t>
+  </si>
+  <si>
+    <t>777422996731755</t>
+  </si>
+  <si>
+    <t>465472391693106</t>
+  </si>
+  <si>
+    <t>777423677128532</t>
+  </si>
+  <si>
+    <t>777423009363641</t>
+  </si>
+  <si>
+    <t>777423648422955</t>
+  </si>
+  <si>
+    <t>79119161828030</t>
+  </si>
+  <si>
+    <t>79119122374228</t>
+  </si>
+  <si>
+    <t>9817726965432</t>
+  </si>
+  <si>
+    <t>79118705036709</t>
+  </si>
+  <si>
+    <t>777423955269542</t>
+  </si>
+  <si>
+    <t>465475481375138</t>
   </si>
 </sst>
 </file>
@@ -310,10 +538,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -836,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -1243,6 +1477,386 @@
     <row r="79" spans="1:1">
       <c r="A79" s="3" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="256">
   <si>
     <t>Track</t>
   </si>
@@ -478,6 +478,312 @@
   </si>
   <si>
     <t>465475481375138</t>
+  </si>
+  <si>
+    <t>777424220162412</t>
+  </si>
+  <si>
+    <t>465478890570558</t>
+  </si>
+  <si>
+    <t>465478836046637</t>
+  </si>
+  <si>
+    <t>YT8883903450609</t>
+  </si>
+  <si>
+    <t>JT5502579705752</t>
+  </si>
+  <si>
+    <t>777424450392984</t>
+  </si>
+  <si>
+    <t>777423915519907</t>
+  </si>
+  <si>
+    <t>YT8883891190132</t>
+  </si>
+  <si>
+    <t>79119334943698</t>
+  </si>
+  <si>
+    <t>465478695635802</t>
+  </si>
+  <si>
+    <t>777424019456798</t>
+  </si>
+  <si>
+    <t>465476542484994</t>
+  </si>
+  <si>
+    <t>465469564298701</t>
+  </si>
+  <si>
+    <t>JT5502224005826</t>
+  </si>
+  <si>
+    <t>JT5502578278301</t>
+  </si>
+  <si>
+    <t>JT5502396965926</t>
+  </si>
+  <si>
+    <t>YT8884489615042</t>
+  </si>
+  <si>
+    <t>JT5502242836349</t>
+  </si>
+  <si>
+    <t>YT8883878440548</t>
+  </si>
+  <si>
+    <t>777423993882325</t>
+  </si>
+  <si>
+    <t>777424713674098</t>
+  </si>
+  <si>
+    <t>JT5502298396291</t>
+  </si>
+  <si>
+    <t>YT8884117072986</t>
+  </si>
+  <si>
+    <t>JT5502070896573</t>
+  </si>
+  <si>
+    <t>465471994471730</t>
+  </si>
+  <si>
+    <t>777424752557155</t>
+  </si>
+  <si>
+    <t>JT5502515695069</t>
+  </si>
+  <si>
+    <t>777423826557941</t>
+  </si>
+  <si>
+    <t>465480645383240</t>
+  </si>
+  <si>
+    <t>JT5503266812933</t>
+  </si>
+  <si>
+    <t>79120332036445</t>
+  </si>
+  <si>
+    <t>465473534442564</t>
+  </si>
+  <si>
+    <t>465470049614367</t>
+  </si>
+  <si>
+    <t>YT8883878678840</t>
+  </si>
+  <si>
+    <t>JT5502695633268</t>
+  </si>
+  <si>
+    <t>79120061027112</t>
+  </si>
+  <si>
+    <t>YT8884336503775</t>
+  </si>
+  <si>
+    <t>79119935578123</t>
+  </si>
+  <si>
+    <t>79119902597646</t>
+  </si>
+  <si>
+    <t>9817844495105</t>
+  </si>
+  <si>
+    <t>79119333092366</t>
+  </si>
+  <si>
+    <t>465481632912782</t>
+  </si>
+  <si>
+    <t>777424342650506</t>
+  </si>
+  <si>
+    <t>JT5502741718081</t>
+  </si>
+  <si>
+    <t>79119623086735</t>
+  </si>
+  <si>
+    <t>JT5502253986072</t>
+  </si>
+  <si>
+    <t>JT5502750696507</t>
+  </si>
+  <si>
+    <t>79119364223825</t>
+  </si>
+  <si>
+    <t>YT8883932774068</t>
+  </si>
+  <si>
+    <t>9817833727780</t>
+  </si>
+  <si>
+    <t>79119682173315</t>
+  </si>
+  <si>
+    <t>465478907911956</t>
+  </si>
+  <si>
+    <t>79016454897614</t>
+  </si>
+  <si>
+    <t>79119373863903</t>
+  </si>
+  <si>
+    <t>79119699371877</t>
+  </si>
+  <si>
+    <t>9817814907148</t>
+  </si>
+  <si>
+    <t>79120384923273</t>
+  </si>
+  <si>
+    <t>777424230198347</t>
+  </si>
+  <si>
+    <t>9817817261348</t>
+  </si>
+  <si>
+    <t>JT5502063985498</t>
+  </si>
+  <si>
+    <t>79119416390403</t>
+  </si>
+  <si>
+    <t>79120038283526</t>
+  </si>
+  <si>
+    <t>79119353172438</t>
+  </si>
+  <si>
+    <t>9817817233388</t>
+  </si>
+  <si>
+    <t>JT9001357075546</t>
+  </si>
+  <si>
+    <t>9817802550951</t>
+  </si>
+  <si>
+    <t>YT8884389671506</t>
+  </si>
+  <si>
+    <t>JT5502803401712</t>
+  </si>
+  <si>
+    <t>465480494417993</t>
+  </si>
+  <si>
+    <t>YT8883889378511</t>
+  </si>
+  <si>
+    <t>JT5501949529727</t>
+  </si>
+  <si>
+    <t>9817783262947</t>
+  </si>
+  <si>
+    <t>777424563328445</t>
+  </si>
+  <si>
+    <t>JT5502586459458</t>
+  </si>
+  <si>
+    <t>JT5502038877683</t>
+  </si>
+  <si>
+    <t>777424953542826</t>
+  </si>
+  <si>
+    <t>79119680373126</t>
+  </si>
+  <si>
+    <t>9817833357257</t>
+  </si>
+  <si>
+    <t>9817744360683</t>
+  </si>
+  <si>
+    <t>9817824222503</t>
+  </si>
+  <si>
+    <t>9817842086178</t>
+  </si>
+  <si>
+    <t>YT8884426509513</t>
+  </si>
+  <si>
+    <t>465478784045939</t>
+  </si>
+  <si>
+    <t>79120061484942</t>
+  </si>
+  <si>
+    <t>79016630818351</t>
+  </si>
+  <si>
+    <t>777424241079598</t>
+  </si>
+  <si>
+    <t>465482477918590</t>
+  </si>
+  <si>
+    <t>YT8884120626190</t>
+  </si>
+  <si>
+    <t>YT8884258229922</t>
+  </si>
+  <si>
+    <t>JT3169425015783</t>
+  </si>
+  <si>
+    <t>777424168124852</t>
+  </si>
+  <si>
+    <t>9817726240838</t>
+  </si>
+  <si>
+    <t>79120328238119</t>
+  </si>
+  <si>
+    <t>79120018634046</t>
+  </si>
+  <si>
+    <t>JT5502797492566</t>
+  </si>
+  <si>
+    <t>YT8883447163830</t>
+  </si>
+  <si>
+    <t>79119513045156</t>
+  </si>
+  <si>
+    <t>777424993812033</t>
+  </si>
+  <si>
+    <t>465476500993347</t>
+  </si>
+  <si>
+    <t>777424361174079</t>
+  </si>
+  <si>
+    <t>9817874570506</t>
+  </si>
+  <si>
+    <t>465479229384518</t>
   </si>
 </sst>
 </file>
@@ -538,10 +844,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1070,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D259"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -1857,6 +2169,526 @@
     <row r="155" spans="1:1">
       <c r="A155" s="4" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="7" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="7" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Track</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>JT5505255975481</t>
+  </si>
+  <si>
+    <t>JT3169788112207</t>
   </si>
 </sst>
 </file>
@@ -1078,10 +1081,14 @@
       <c r="A112" s="3"/>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="3"/>
+      <c r="A113" s="3">
+        <v>777425546939086</v>
+      </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="3"/>
+      <c r="A114" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="3"/>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="110">
   <si>
     <t>Track</t>
   </si>
@@ -27,115 +27,325 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>YT7632675835236</t>
-  </si>
-  <si>
-    <t>9817955045050</t>
-  </si>
-  <si>
-    <t>9817966082788</t>
-  </si>
-  <si>
-    <t>YT8885905743570</t>
-  </si>
-  <si>
-    <t>777426806685057</t>
-  </si>
-  <si>
-    <t>79121799191425</t>
-  </si>
-  <si>
-    <t>9817971903882</t>
-  </si>
-  <si>
-    <t>79121608498840</t>
-  </si>
-  <si>
-    <t>79121527527448</t>
-  </si>
-  <si>
-    <t>465501494935518</t>
-  </si>
-  <si>
-    <t>9817956925032</t>
-  </si>
-  <si>
-    <t>9817958820639</t>
-  </si>
-  <si>
-    <t>JT5505201778852</t>
-  </si>
-  <si>
-    <t>79121981513759</t>
-  </si>
-  <si>
-    <t>79121727019157</t>
-  </si>
-  <si>
-    <t>9817966084147</t>
-  </si>
-  <si>
-    <t>9817943793166</t>
-  </si>
-  <si>
-    <t>9817954030235</t>
-  </si>
-  <si>
-    <t>YT8886196738528</t>
-  </si>
-  <si>
-    <t>79121667178404</t>
-  </si>
-  <si>
-    <t>YT8885969781930</t>
-  </si>
-  <si>
-    <t>777426778488134</t>
-  </si>
-  <si>
-    <t>9817951581468</t>
-  </si>
-  <si>
-    <t>465502104232434</t>
-  </si>
-  <si>
-    <t>777426457494875</t>
-  </si>
-  <si>
-    <t>465500678686356</t>
-  </si>
-  <si>
-    <t>JT5505282889514</t>
-  </si>
-  <si>
-    <t>79121800010852</t>
-  </si>
-  <si>
-    <t>777426502141976</t>
-  </si>
-  <si>
-    <t>79121636735126</t>
-  </si>
-  <si>
-    <t>465501199601972</t>
-  </si>
-  <si>
-    <t>JT5504998948258</t>
-  </si>
-  <si>
-    <t>9817949573418</t>
-  </si>
-  <si>
-    <t>79121618345607</t>
-  </si>
-  <si>
-    <t>JT5504825809292</t>
-  </si>
-  <si>
-    <t>JT5505255975481</t>
-  </si>
-  <si>
-    <t>JT3169788112207</t>
+    <t>79122498404692</t>
+  </si>
+  <si>
+    <t>79122824512889</t>
+  </si>
+  <si>
+    <t>JT5504942213349</t>
+  </si>
+  <si>
+    <t>465503689108873</t>
+  </si>
+  <si>
+    <t>YT8886384406516</t>
+  </si>
+  <si>
+    <t>777426672106640</t>
+  </si>
+  <si>
+    <t>465508194640408</t>
+  </si>
+  <si>
+    <t>YT8886672643157</t>
+  </si>
+  <si>
+    <t>YT8886765884971</t>
+  </si>
+  <si>
+    <t>79122239505024</t>
+  </si>
+  <si>
+    <t>465502154312880</t>
+  </si>
+  <si>
+    <t>79122531626386</t>
+  </si>
+  <si>
+    <t>JT5505439599036</t>
+  </si>
+  <si>
+    <t>777427346837197</t>
+  </si>
+  <si>
+    <t>465509376161976</t>
+  </si>
+  <si>
+    <t>JT5506545455404</t>
+  </si>
+  <si>
+    <t>9818062333520</t>
+  </si>
+  <si>
+    <t>YT8885952562674</t>
+  </si>
+  <si>
+    <t>777427087637042</t>
+  </si>
+  <si>
+    <t>465509754781473</t>
+  </si>
+  <si>
+    <t>79122940553887</t>
+  </si>
+  <si>
+    <t>79122143971445</t>
+  </si>
+  <si>
+    <t>777426587500268</t>
+  </si>
+  <si>
+    <t>YT8886581615609</t>
+  </si>
+  <si>
+    <t>79122539705596</t>
+  </si>
+  <si>
+    <t>JT5504307209131</t>
+  </si>
+  <si>
+    <t>JT5504307726856</t>
+  </si>
+  <si>
+    <t>465500863123295</t>
+  </si>
+  <si>
+    <t>9817997645724</t>
+  </si>
+  <si>
+    <t>777427358319738</t>
+  </si>
+  <si>
+    <t>JT5505709983398</t>
+  </si>
+  <si>
+    <t>JT5505149288184</t>
+  </si>
+  <si>
+    <t>465507254476899</t>
+  </si>
+  <si>
+    <t>465508782347677</t>
+  </si>
+  <si>
+    <t>JT5505589725403</t>
+  </si>
+  <si>
+    <t>79122258818446</t>
+  </si>
+  <si>
+    <t>YT8885333846328</t>
+  </si>
+  <si>
+    <t>YT7632094972824</t>
+  </si>
+  <si>
+    <t>YT7633058282366</t>
+  </si>
+  <si>
+    <t>465492724651609</t>
+  </si>
+  <si>
+    <t>YT7632865500214</t>
+  </si>
+  <si>
+    <t>73717328976746</t>
+  </si>
+  <si>
+    <t>79122191195930</t>
+  </si>
+  <si>
+    <t>JT5505896621144</t>
+  </si>
+  <si>
+    <t>YT8887180283699</t>
+  </si>
+  <si>
+    <t>YT8886635357071</t>
+  </si>
+  <si>
+    <t>465506921261332</t>
+  </si>
+  <si>
+    <t>9818049060949</t>
+  </si>
+  <si>
+    <t>777426896912398</t>
+  </si>
+  <si>
+    <t>YT8886915531472</t>
+  </si>
+  <si>
+    <t>JT5505595034152</t>
+  </si>
+  <si>
+    <t>465506506662766</t>
+  </si>
+  <si>
+    <t>JT5505661002107</t>
+  </si>
+  <si>
+    <t>79122909191923</t>
+  </si>
+  <si>
+    <t>465514633151567</t>
+  </si>
+  <si>
+    <t>JT5505607338561</t>
+  </si>
+  <si>
+    <t>9817961258666</t>
+  </si>
+  <si>
+    <t>465502961247710</t>
+  </si>
+  <si>
+    <t>YT8886715622217</t>
+  </si>
+  <si>
+    <t>YT7632553701941</t>
+  </si>
+  <si>
+    <t>YT7632865575296</t>
+  </si>
+  <si>
+    <t>465514489030346</t>
+  </si>
+  <si>
+    <t>777427085931458</t>
+  </si>
+  <si>
+    <t>465507914083094</t>
+  </si>
+  <si>
+    <t>79122173802535</t>
+  </si>
+  <si>
+    <t>YT8887474259342</t>
+  </si>
+  <si>
+    <t>9818042527494</t>
+  </si>
+  <si>
+    <t>777426842208139</t>
+  </si>
+  <si>
+    <t>JT5505842113414</t>
+  </si>
+  <si>
+    <t>9818049917828</t>
+  </si>
+  <si>
+    <t>9818058273226</t>
+  </si>
+  <si>
+    <t>79122934811109</t>
+  </si>
+  <si>
+    <t>79122687747282</t>
+  </si>
+  <si>
+    <t>465514247899696</t>
+  </si>
+  <si>
+    <t>777427186380345</t>
+  </si>
+  <si>
+    <t>YT8887499234380</t>
+  </si>
+  <si>
+    <t>JT5505044125581</t>
+  </si>
+  <si>
+    <t>79122847348936</t>
+  </si>
+  <si>
+    <t>777426933997095</t>
+  </si>
+  <si>
+    <t>465503371714135</t>
+  </si>
+  <si>
+    <t>JT5504948725054</t>
+  </si>
+  <si>
+    <t>79122602798414</t>
+  </si>
+  <si>
+    <t>465506370218522</t>
+  </si>
+  <si>
+    <t>JT5504898039627</t>
+  </si>
+  <si>
+    <t>8244401142220</t>
+  </si>
+  <si>
+    <t>465507898194276</t>
+  </si>
+  <si>
+    <t>777427144833852</t>
+  </si>
+  <si>
+    <t>JT5504948709547</t>
+  </si>
+  <si>
+    <t>JT5505554534455</t>
+  </si>
+  <si>
+    <t>465506538373629</t>
+  </si>
+  <si>
+    <t>465499311973338</t>
+  </si>
+  <si>
+    <t>777426918928394</t>
+  </si>
+  <si>
+    <t>JT5504985858847</t>
+  </si>
+  <si>
+    <t>435270971367024</t>
+  </si>
+  <si>
+    <t>465508083387532</t>
+  </si>
+  <si>
+    <t>465496611398797</t>
+  </si>
+  <si>
+    <t>79122903499256</t>
+  </si>
+  <si>
+    <t>YT8887233456818</t>
+  </si>
+  <si>
+    <t>9817995428423</t>
+  </si>
+  <si>
+    <t>465509360373029</t>
+  </si>
+  <si>
+    <t>465509132293841</t>
+  </si>
+  <si>
+    <t>YT8886995204480</t>
+  </si>
+  <si>
+    <t>777427404579120</t>
+  </si>
+  <si>
+    <t>YT8887110380694</t>
+  </si>
+  <si>
+    <t>JT5505579885426</t>
+  </si>
+  <si>
+    <t>JT3170316758166</t>
+  </si>
+  <si>
+    <t>79018771858616</t>
   </si>
 </sst>
 </file>
@@ -196,13 +406,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -728,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -748,551 +955,575 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="3"/>
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="3"/>
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="3"/>
+      <c r="A7" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="3"/>
+      <c r="A8" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="2"/>
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="3"/>
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="2"/>
+      <c r="A11" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="2"/>
+      <c r="A12" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="3"/>
+      <c r="A13" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="3"/>
+      <c r="A15" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="3"/>
+      <c r="A16" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="2"/>
+      <c r="A18" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="3"/>
+      <c r="A20" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="2"/>
+      <c r="A21" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="3"/>
+      <c r="A22" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="3"/>
+      <c r="A23" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="3"/>
+      <c r="A24" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="2"/>
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="3"/>
+      <c r="A26" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="2"/>
+      <c r="A27" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="2"/>
+      <c r="A28" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="2"/>
+      <c r="A29" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="3"/>
+      <c r="A30" s="4" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="2"/>
+      <c r="A31" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="2"/>
+      <c r="A32" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="2"/>
+      <c r="A33" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="3"/>
+      <c r="A34" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="2"/>
+      <c r="A35" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="2"/>
+      <c r="A36" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="3"/>
+      <c r="A37" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="2"/>
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="2"/>
+      <c r="A39" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="3"/>
+      <c r="A40" s="3" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="3"/>
+      <c r="A41" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="3"/>
+      <c r="A42" s="3" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="2"/>
+      <c r="A43" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="2"/>
+      <c r="A44" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="2"/>
+      <c r="A45" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="3"/>
+      <c r="A46" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="3"/>
+      <c r="A47" s="3" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="3"/>
+      <c r="A48" s="4" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="2"/>
+      <c r="A49" s="4" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="3"/>
+      <c r="A50" s="4" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="3"/>
+      <c r="A51" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="3"/>
+      <c r="A52" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="3"/>
+      <c r="A53" s="4" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="3"/>
+      <c r="A54" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="3"/>
+      <c r="A55" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="2"/>
+      <c r="A56" s="4" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="2"/>
+      <c r="A57" s="3" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="3"/>
+      <c r="A58" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="2"/>
+      <c r="A59" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="3"/>
+      <c r="A60" s="3" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="3"/>
+      <c r="A61" s="3" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="3"/>
+      <c r="A62" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="3"/>
+      <c r="A63" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="2"/>
+      <c r="A64" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="2"/>
+      <c r="A65" s="4" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="2"/>
+      <c r="A66" s="4" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="3"/>
+      <c r="A67" s="3" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="2"/>
+      <c r="A68" s="4" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="3"/>
+      <c r="A69" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="3"/>
+      <c r="A70" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="3"/>
+      <c r="A71" s="4" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="2"/>
+      <c r="A72" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="2"/>
+      <c r="A73" s="4" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="2"/>
+      <c r="A74" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="3"/>
+      <c r="A75" s="4" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="2"/>
+      <c r="A76" s="4" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="2"/>
+      <c r="A77" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="3"/>
+      <c r="A78" s="3" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="3"/>
+      <c r="A79" s="4" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="3"/>
+      <c r="A80" s="4" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="2"/>
+      <c r="A81" s="4" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="3"/>
+      <c r="A82" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="3"/>
+      <c r="A83" s="4" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="3"/>
+      <c r="A84" s="4" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="3"/>
+      <c r="A85" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="2"/>
+      <c r="A86" s="3" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="2"/>
+      <c r="A87" s="4" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="3"/>
+      <c r="A88" s="4" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="2"/>
+      <c r="A89" s="4" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="3"/>
+      <c r="A90" s="4" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="3"/>
+      <c r="A91" s="4" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="3"/>
+      <c r="A92" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="3"/>
+      <c r="A93" s="3" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="3"/>
+      <c r="A94" s="4" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="3"/>
+      <c r="A95" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="3"/>
+      <c r="A96" s="4" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="2"/>
+      <c r="A97" s="3" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="3"/>
+      <c r="A98" s="4" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="3"/>
+      <c r="A99" s="4" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="3"/>
+      <c r="A100" s="4" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="3"/>
+      <c r="A101" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="3"/>
+      <c r="A102" s="3" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="3"/>
+      <c r="A103" s="4" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="2"/>
+      <c r="A104" s="4" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="3"/>
+      <c r="A105" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="3"/>
+      <c r="A106" s="3" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="3"/>
+      <c r="A107" s="4" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="3"/>
+      <c r="A108" s="3" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="3"/>
+      <c r="A109" s="3" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="3"/>
+      <c r="A110" s="3" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="2"/>
+      <c r="A111" s="4" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="3"/>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="3">
-        <v>777425546939086</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="3" t="s">
-        <v>39</v>
-      </c>
+      <c r="A112" s="2"/>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="3"/>
+      <c r="A115" s="2"/>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="3"/>
+      <c r="A116" s="2"/>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="3"/>
+      <c r="A117" s="2"/>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="3"/>
+      <c r="A118" s="2"/>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="3"/>
+      <c r="A119" s="2"/>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="3"/>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="3"/>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="3"/>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="4" t="s">
-        <v>38</v>
-      </c>
+      <c r="A120" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
   <si>
     <t>Track</t>
   </si>
@@ -25,6 +25,228 @@
   </si>
   <si>
     <t>DATE</t>
+  </si>
+  <si>
+    <t>465511136676140</t>
+  </si>
+  <si>
+    <t>YT8887569556680</t>
+  </si>
+  <si>
+    <t>YT8888537584100</t>
+  </si>
+  <si>
+    <t>777427507401185</t>
+  </si>
+  <si>
+    <t>YT8888515293154</t>
+  </si>
+  <si>
+    <t>777428637814555</t>
+  </si>
+  <si>
+    <t>777428378951961</t>
+  </si>
+  <si>
+    <t>465510505044154</t>
+  </si>
+  <si>
+    <t>JT5507244554173</t>
+  </si>
+  <si>
+    <t>JT9001570009876</t>
+  </si>
+  <si>
+    <t>777427548979794</t>
+  </si>
+  <si>
+    <t>777427562006041</t>
+  </si>
+  <si>
+    <t>777427997167390</t>
+  </si>
+  <si>
+    <t>465514871468417</t>
+  </si>
+  <si>
+    <t>777427584520146</t>
+  </si>
+  <si>
+    <t>YT8887562635203</t>
+  </si>
+  <si>
+    <t>465514444026213</t>
+  </si>
+  <si>
+    <t>465505840210088</t>
+  </si>
+  <si>
+    <t>465516060265840</t>
+  </si>
+  <si>
+    <t>777427923003751</t>
+  </si>
+  <si>
+    <t>JT5505794604522</t>
+  </si>
+  <si>
+    <t>JT9001576894302</t>
+  </si>
+  <si>
+    <t>465504078480174</t>
+  </si>
+  <si>
+    <t>JT5506418660495</t>
+  </si>
+  <si>
+    <t>YT8887501949475</t>
+  </si>
+  <si>
+    <t>JT5506336304725</t>
+  </si>
+  <si>
+    <t>JT5506179560811</t>
+  </si>
+  <si>
+    <t>465510240057912</t>
+  </si>
+  <si>
+    <t>777427938573474</t>
+  </si>
+  <si>
+    <t>JT5506658558624</t>
+  </si>
+  <si>
+    <t>777427933079050</t>
+  </si>
+  <si>
+    <t>465513976759928</t>
+  </si>
+  <si>
+    <t>YT8887716104052</t>
+  </si>
+  <si>
+    <t>YT8887558230557</t>
+  </si>
+  <si>
+    <t>79123182559533</t>
+  </si>
+  <si>
+    <t>JT5506461519158</t>
+  </si>
+  <si>
+    <t>465505833882627</t>
+  </si>
+  <si>
+    <t>JT5506173436073</t>
+  </si>
+  <si>
+    <t>YT8887415841436</t>
+  </si>
+  <si>
+    <t>465514648477851</t>
+  </si>
+  <si>
+    <t>YT8887564921339</t>
+  </si>
+  <si>
+    <t>777428024999640</t>
+  </si>
+  <si>
+    <t>773432034780670</t>
+  </si>
+  <si>
+    <t>JT5506221766106</t>
+  </si>
+  <si>
+    <t>JT5506232592542</t>
+  </si>
+  <si>
+    <t>JT5507324542496</t>
+  </si>
+  <si>
+    <t>79123085410794</t>
+  </si>
+  <si>
+    <t>JT5506626995922</t>
+  </si>
+  <si>
+    <t>JT5507237177763</t>
+  </si>
+  <si>
+    <t>JT5506307113595</t>
+  </si>
+  <si>
+    <t>YT8888105378643</t>
+  </si>
+  <si>
+    <t>79123098652802</t>
+  </si>
+  <si>
+    <t>777427962413779</t>
+  </si>
+  <si>
+    <t>465514479319672</t>
+  </si>
+  <si>
+    <t>777427958247663</t>
+  </si>
+  <si>
+    <t>YT8887865004609</t>
+  </si>
+  <si>
+    <t>79123114287214</t>
+  </si>
+  <si>
+    <t>79123570328412</t>
+  </si>
+  <si>
+    <t>435274435411742</t>
+  </si>
+  <si>
+    <t>79123252656006</t>
+  </si>
+  <si>
+    <t>JT5506186308031</t>
+  </si>
+  <si>
+    <t>79123106747998</t>
+  </si>
+  <si>
+    <t>JT5507203669617</t>
+  </si>
+  <si>
+    <t>777427612934180</t>
+  </si>
+  <si>
+    <t>79123239816408</t>
+  </si>
+  <si>
+    <t>777428182458625</t>
+  </si>
+  <si>
+    <t>JT5507276114172</t>
+  </si>
+  <si>
+    <t>777427635693095</t>
+  </si>
+  <si>
+    <t>79123166392831</t>
+  </si>
+  <si>
+    <t>465515646672564</t>
+  </si>
+  <si>
+    <t>777428265484423</t>
+  </si>
+  <si>
+    <t>79019435474422</t>
+  </si>
+  <si>
+    <t>JT5507337898487</t>
+  </si>
+  <si>
+    <t>465510460307851</t>
   </si>
 </sst>
 </file>
@@ -85,10 +307,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -627,6 +855,381 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
     <row r="112" spans="1:1">
       <c r="A112" s="2"/>
     </row>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="138">
   <si>
     <t>Track</t>
   </si>
@@ -247,6 +247,189 @@
   </si>
   <si>
     <t>465510460307851</t>
+  </si>
+  <si>
+    <t>9818135183313</t>
+  </si>
+  <si>
+    <t>YT8888060085600</t>
+  </si>
+  <si>
+    <t>777428624964212</t>
+  </si>
+  <si>
+    <t>JT5506803649727</t>
+  </si>
+  <si>
+    <t>YT8887969967981</t>
+  </si>
+  <si>
+    <t>777428482644970</t>
+  </si>
+  <si>
+    <t>465520579629016</t>
+  </si>
+  <si>
+    <t>JT5507113656781</t>
+  </si>
+  <si>
+    <t>777428636239359</t>
+  </si>
+  <si>
+    <t>465517949919201</t>
+  </si>
+  <si>
+    <t>YT8888426812721</t>
+  </si>
+  <si>
+    <t>79123707154281</t>
+  </si>
+  <si>
+    <t>79123535621138</t>
+  </si>
+  <si>
+    <t>9818141869938</t>
+  </si>
+  <si>
+    <t>9818139113611</t>
+  </si>
+  <si>
+    <t>465517769716193</t>
+  </si>
+  <si>
+    <t>YT8888253835016</t>
+  </si>
+  <si>
+    <t>YT8889172189248</t>
+  </si>
+  <si>
+    <t>465521950123855</t>
+  </si>
+  <si>
+    <t>777428509196955</t>
+  </si>
+  <si>
+    <t>9818122256458</t>
+  </si>
+  <si>
+    <t>9818110603935</t>
+  </si>
+  <si>
+    <t>JT5506823984702</t>
+  </si>
+  <si>
+    <t>465521357894421</t>
+  </si>
+  <si>
+    <t>9818114512539</t>
+  </si>
+  <si>
+    <t>9818143746867</t>
+  </si>
+  <si>
+    <t>YT8888324621641</t>
+  </si>
+  <si>
+    <t>777428534262087</t>
+  </si>
+  <si>
+    <t>9818138403691</t>
+  </si>
+  <si>
+    <t>9818106766725</t>
+  </si>
+  <si>
+    <t>9818127090526</t>
+  </si>
+  <si>
+    <t>9818187182439</t>
+  </si>
+  <si>
+    <t>YT8888308339274</t>
+  </si>
+  <si>
+    <t>777428218867597</t>
+  </si>
+  <si>
+    <t>79123395536493</t>
+  </si>
+  <si>
+    <t>9818093298447</t>
+  </si>
+  <si>
+    <t>465520446419119</t>
+  </si>
+  <si>
+    <t>9818091703204</t>
+  </si>
+  <si>
+    <t>79123665608643</t>
+  </si>
+  <si>
+    <t>777428489819234</t>
+  </si>
+  <si>
+    <t>9818082414629</t>
+  </si>
+  <si>
+    <t>9818070555800</t>
+  </si>
+  <si>
+    <t>9818116933963</t>
+  </si>
+  <si>
+    <t>79123488727326</t>
+  </si>
+  <si>
+    <t>777427625098257</t>
+  </si>
+  <si>
+    <t>773432223697761</t>
+  </si>
+  <si>
+    <t>9818122486430</t>
+  </si>
+  <si>
+    <t>9818180980604</t>
+  </si>
+  <si>
+    <t>9818111039401</t>
+  </si>
+  <si>
+    <t>9818172123217</t>
+  </si>
+  <si>
+    <t>JT5507144076361</t>
+  </si>
+  <si>
+    <t>9818138761106</t>
+  </si>
+  <si>
+    <t>9818180581994</t>
+  </si>
+  <si>
+    <t>79123798032324</t>
+  </si>
+  <si>
+    <t>79019659011425</t>
+  </si>
+  <si>
+    <t>465522915619192</t>
+  </si>
+  <si>
+    <t>9818072983732</t>
+  </si>
+  <si>
+    <t>777428444129030</t>
+  </si>
+  <si>
+    <t>9818093692863</t>
+  </si>
+  <si>
+    <t>21.07.26</t>
+  </si>
+  <si>
+    <t>19.07.26</t>
   </si>
 </sst>
 </file>
@@ -307,10 +490,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -836,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -856,400 +1042,684 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="3" t="s">
+    <row r="65" spans="1:2">
+      <c r="A65" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="4" t="s">
+    <row r="66" spans="1:2">
+      <c r="A66" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="4" t="s">
+    <row r="67" spans="1:2">
+      <c r="A67" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="4" t="s">
+    <row r="68" spans="1:2">
+      <c r="A68" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="3" t="s">
+    <row r="69" spans="1:2">
+      <c r="A69" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="4" t="s">
+    <row r="70" spans="1:2">
+      <c r="A70" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="4" t="s">
+    <row r="71" spans="1:2">
+      <c r="A71" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="4" t="s">
+    <row r="72" spans="1:2">
+      <c r="A72" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="4" t="s">
+    <row r="73" spans="1:2">
+      <c r="A73" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="4" t="s">
+    <row r="74" spans="1:2">
+      <c r="A74" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="3" t="s">
+    <row r="75" spans="1:2">
+      <c r="A75" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="4" t="s">
+    <row r="76" spans="1:2">
+      <c r="A76" s="3" t="s">
         <v>76</v>
       </c>
     </row>
+    <row r="77" spans="1:2">
+      <c r="B77" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="2"/>
+      <c r="A112" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="5" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="2"/>
+      <c r="A115" s="5" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="2"/>
+      <c r="A116" s="5" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="2"/>
+      <c r="A117" s="5" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="2"/>
+      <c r="A118" s="5" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="2"/>
+      <c r="A119" s="5" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="2"/>
+      <c r="A120" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="B137" t="s">
+        <v>136</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
   <si>
     <t>Track</t>
   </si>
@@ -27,409 +27,229 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>465511136676140</t>
-  </si>
-  <si>
-    <t>YT8887569556680</t>
-  </si>
-  <si>
-    <t>YT8888537584100</t>
-  </si>
-  <si>
-    <t>777427507401185</t>
-  </si>
-  <si>
-    <t>YT8888515293154</t>
-  </si>
-  <si>
-    <t>777428637814555</t>
-  </si>
-  <si>
-    <t>777428378951961</t>
-  </si>
-  <si>
-    <t>465510505044154</t>
-  </si>
-  <si>
-    <t>JT5507244554173</t>
-  </si>
-  <si>
-    <t>JT9001570009876</t>
-  </si>
-  <si>
-    <t>777427548979794</t>
-  </si>
-  <si>
-    <t>777427562006041</t>
-  </si>
-  <si>
-    <t>777427997167390</t>
-  </si>
-  <si>
-    <t>465514871468417</t>
-  </si>
-  <si>
-    <t>777427584520146</t>
-  </si>
-  <si>
-    <t>YT8887562635203</t>
-  </si>
-  <si>
-    <t>465514444026213</t>
-  </si>
-  <si>
-    <t>465505840210088</t>
-  </si>
-  <si>
-    <t>465516060265840</t>
-  </si>
-  <si>
-    <t>777427923003751</t>
-  </si>
-  <si>
-    <t>JT5505794604522</t>
-  </si>
-  <si>
-    <t>JT9001576894302</t>
-  </si>
-  <si>
-    <t>465504078480174</t>
-  </si>
-  <si>
-    <t>JT5506418660495</t>
-  </si>
-  <si>
-    <t>YT8887501949475</t>
-  </si>
-  <si>
-    <t>JT5506336304725</t>
-  </si>
-  <si>
-    <t>JT5506179560811</t>
-  </si>
-  <si>
-    <t>465510240057912</t>
-  </si>
-  <si>
-    <t>777427938573474</t>
-  </si>
-  <si>
-    <t>JT5506658558624</t>
-  </si>
-  <si>
-    <t>777427933079050</t>
-  </si>
-  <si>
-    <t>465513976759928</t>
-  </si>
-  <si>
-    <t>YT8887716104052</t>
-  </si>
-  <si>
-    <t>YT8887558230557</t>
-  </si>
-  <si>
-    <t>79123182559533</t>
-  </si>
-  <si>
-    <t>JT5506461519158</t>
-  </si>
-  <si>
-    <t>465505833882627</t>
-  </si>
-  <si>
-    <t>JT5506173436073</t>
-  </si>
-  <si>
-    <t>YT8887415841436</t>
-  </si>
-  <si>
-    <t>465514648477851</t>
-  </si>
-  <si>
-    <t>YT8887564921339</t>
-  </si>
-  <si>
-    <t>777428024999640</t>
-  </si>
-  <si>
-    <t>773432034780670</t>
-  </si>
-  <si>
-    <t>JT5506221766106</t>
-  </si>
-  <si>
-    <t>JT5506232592542</t>
-  </si>
-  <si>
-    <t>JT5507324542496</t>
-  </si>
-  <si>
-    <t>79123085410794</t>
-  </si>
-  <si>
-    <t>JT5506626995922</t>
-  </si>
-  <si>
-    <t>JT5507237177763</t>
-  </si>
-  <si>
-    <t>JT5506307113595</t>
-  </si>
-  <si>
-    <t>YT8888105378643</t>
-  </si>
-  <si>
-    <t>79123098652802</t>
-  </si>
-  <si>
-    <t>777427962413779</t>
-  </si>
-  <si>
-    <t>465514479319672</t>
-  </si>
-  <si>
-    <t>777427958247663</t>
-  </si>
-  <si>
-    <t>YT8887865004609</t>
-  </si>
-  <si>
-    <t>79123114287214</t>
-  </si>
-  <si>
-    <t>79123570328412</t>
-  </si>
-  <si>
-    <t>435274435411742</t>
-  </si>
-  <si>
-    <t>79123252656006</t>
-  </si>
-  <si>
-    <t>JT5506186308031</t>
-  </si>
-  <si>
-    <t>79123106747998</t>
-  </si>
-  <si>
-    <t>JT5507203669617</t>
-  </si>
-  <si>
-    <t>777427612934180</t>
-  </si>
-  <si>
-    <t>79123239816408</t>
-  </si>
-  <si>
-    <t>777428182458625</t>
-  </si>
-  <si>
-    <t>JT5507276114172</t>
-  </si>
-  <si>
-    <t>777427635693095</t>
-  </si>
-  <si>
-    <t>79123166392831</t>
-  </si>
-  <si>
-    <t>465515646672564</t>
-  </si>
-  <si>
-    <t>777428265484423</t>
-  </si>
-  <si>
-    <t>79019435474422</t>
-  </si>
-  <si>
-    <t>JT5507337898487</t>
-  </si>
-  <si>
-    <t>465510460307851</t>
-  </si>
-  <si>
-    <t>9818135183313</t>
-  </si>
-  <si>
-    <t>YT8888060085600</t>
-  </si>
-  <si>
-    <t>777428624964212</t>
-  </si>
-  <si>
-    <t>JT5506803649727</t>
-  </si>
-  <si>
-    <t>YT8887969967981</t>
-  </si>
-  <si>
-    <t>777428482644970</t>
-  </si>
-  <si>
-    <t>465520579629016</t>
-  </si>
-  <si>
-    <t>JT5507113656781</t>
-  </si>
-  <si>
-    <t>777428636239359</t>
-  </si>
-  <si>
-    <t>465517949919201</t>
-  </si>
-  <si>
-    <t>YT8888426812721</t>
-  </si>
-  <si>
-    <t>79123707154281</t>
-  </si>
-  <si>
-    <t>79123535621138</t>
-  </si>
-  <si>
-    <t>9818141869938</t>
-  </si>
-  <si>
-    <t>9818139113611</t>
-  </si>
-  <si>
-    <t>465517769716193</t>
-  </si>
-  <si>
-    <t>YT8888253835016</t>
-  </si>
-  <si>
-    <t>YT8889172189248</t>
-  </si>
-  <si>
-    <t>465521950123855</t>
-  </si>
-  <si>
-    <t>777428509196955</t>
-  </si>
-  <si>
-    <t>9818122256458</t>
-  </si>
-  <si>
-    <t>9818110603935</t>
-  </si>
-  <si>
-    <t>JT5506823984702</t>
-  </si>
-  <si>
-    <t>465521357894421</t>
-  </si>
-  <si>
-    <t>9818114512539</t>
-  </si>
-  <si>
-    <t>9818143746867</t>
-  </si>
-  <si>
-    <t>YT8888324621641</t>
-  </si>
-  <si>
-    <t>777428534262087</t>
-  </si>
-  <si>
-    <t>9818138403691</t>
-  </si>
-  <si>
-    <t>9818106766725</t>
-  </si>
-  <si>
-    <t>9818127090526</t>
-  </si>
-  <si>
-    <t>9818187182439</t>
-  </si>
-  <si>
-    <t>YT8888308339274</t>
-  </si>
-  <si>
-    <t>777428218867597</t>
-  </si>
-  <si>
-    <t>79123395536493</t>
-  </si>
-  <si>
-    <t>9818093298447</t>
-  </si>
-  <si>
-    <t>465520446419119</t>
-  </si>
-  <si>
-    <t>9818091703204</t>
-  </si>
-  <si>
-    <t>79123665608643</t>
-  </si>
-  <si>
-    <t>777428489819234</t>
-  </si>
-  <si>
-    <t>9818082414629</t>
-  </si>
-  <si>
-    <t>9818070555800</t>
-  </si>
-  <si>
-    <t>9818116933963</t>
-  </si>
-  <si>
-    <t>79123488727326</t>
-  </si>
-  <si>
-    <t>777427625098257</t>
-  </si>
-  <si>
-    <t>773432223697761</t>
-  </si>
-  <si>
-    <t>9818122486430</t>
-  </si>
-  <si>
-    <t>9818180980604</t>
-  </si>
-  <si>
-    <t>9818111039401</t>
-  </si>
-  <si>
-    <t>9818172123217</t>
-  </si>
-  <si>
-    <t>JT5507144076361</t>
-  </si>
-  <si>
-    <t>9818138761106</t>
-  </si>
-  <si>
-    <t>9818180581994</t>
-  </si>
-  <si>
-    <t>79123798032324</t>
-  </si>
-  <si>
-    <t>79019659011425</t>
-  </si>
-  <si>
-    <t>465522915619192</t>
-  </si>
-  <si>
-    <t>9818072983732</t>
-  </si>
-  <si>
-    <t>777428444129030</t>
-  </si>
-  <si>
-    <t>9818093692863</t>
-  </si>
-  <si>
-    <t>21.07.26</t>
-  </si>
-  <si>
-    <t>19.07.26</t>
+    <t>JT5508212661410</t>
+  </si>
+  <si>
+    <t>777429842412690</t>
+  </si>
+  <si>
+    <t>777429216776497</t>
+  </si>
+  <si>
+    <t>465527713805051</t>
+  </si>
+  <si>
+    <t>9818121142515</t>
+  </si>
+  <si>
+    <t>777429406871740</t>
+  </si>
+  <si>
+    <t>777429175898829</t>
+  </si>
+  <si>
+    <t>JT5508278682151</t>
+  </si>
+  <si>
+    <t>465525642438113</t>
+  </si>
+  <si>
+    <t>465528491327470</t>
+  </si>
+  <si>
+    <t>79124536639689</t>
+  </si>
+  <si>
+    <t>YT7634474645487</t>
+  </si>
+  <si>
+    <t>465528254213738</t>
+  </si>
+  <si>
+    <t>465524046250201</t>
+  </si>
+  <si>
+    <t>465528779706963</t>
+  </si>
+  <si>
+    <t>YT8889322954843</t>
+  </si>
+  <si>
+    <t>79124611305565</t>
+  </si>
+  <si>
+    <t>9818236349539</t>
+  </si>
+  <si>
+    <t>79124738593105</t>
+  </si>
+  <si>
+    <t>777429467409312</t>
+  </si>
+  <si>
+    <t>9818166888707</t>
+  </si>
+  <si>
+    <t>79124657949875</t>
+  </si>
+  <si>
+    <t>YT8889372438379</t>
+  </si>
+  <si>
+    <t>JT5508296019212</t>
+  </si>
+  <si>
+    <t>777429819921790</t>
+  </si>
+  <si>
+    <t>79124876732546</t>
+  </si>
+  <si>
+    <t>465526808457050</t>
+  </si>
+  <si>
+    <t>JT5508200550058</t>
+  </si>
+  <si>
+    <t>773433001136488</t>
+  </si>
+  <si>
+    <t>79124505797992</t>
+  </si>
+  <si>
+    <t>9818231853474</t>
+  </si>
+  <si>
+    <t>777429446345891</t>
+  </si>
+  <si>
+    <t>9818246238899</t>
+  </si>
+  <si>
+    <t>JT5508369197851</t>
+  </si>
+  <si>
+    <t>JT5508021872511</t>
+  </si>
+  <si>
+    <t>YT8890208690481</t>
+  </si>
+  <si>
+    <t>79124534861049</t>
+  </si>
+  <si>
+    <t>9818240933564</t>
+  </si>
+  <si>
+    <t>9818231641268</t>
+  </si>
+  <si>
+    <t>9818159442943</t>
+  </si>
+  <si>
+    <t>JT5507816648203</t>
+  </si>
+  <si>
+    <t>465536022619845</t>
+  </si>
+  <si>
+    <t>JT5508405117992</t>
+  </si>
+  <si>
+    <t>YT8889680544962</t>
+  </si>
+  <si>
+    <t>YT8889503886464</t>
+  </si>
+  <si>
+    <t>465535089190368</t>
+  </si>
+  <si>
+    <t>777428987726191</t>
+  </si>
+  <si>
+    <t>777429575873017</t>
+  </si>
+  <si>
+    <t>YT8888878763433</t>
+  </si>
+  <si>
+    <t>777429552673225</t>
+  </si>
+  <si>
+    <t>465525714739882</t>
+  </si>
+  <si>
+    <t>777429440275991</t>
+  </si>
+  <si>
+    <t>777429534217342</t>
+  </si>
+  <si>
+    <t>79125116358608</t>
+  </si>
+  <si>
+    <t>YT8888617717493</t>
+  </si>
+  <si>
+    <t>79125215678036</t>
+  </si>
+  <si>
+    <t>79125103299073</t>
+  </si>
+  <si>
+    <t>465523384478124</t>
+  </si>
+  <si>
+    <t>YT8889407297212</t>
+  </si>
+  <si>
+    <t>465523583671035</t>
+  </si>
+  <si>
+    <t>YT8889363892571</t>
+  </si>
+  <si>
+    <t>777429615568237</t>
+  </si>
+  <si>
+    <t>777430158147321</t>
+  </si>
+  <si>
+    <t>JT5508106864897</t>
+  </si>
+  <si>
+    <t>JT5508317923472</t>
+  </si>
+  <si>
+    <t>777429764323295</t>
+  </si>
+  <si>
+    <t>8218216547421</t>
+  </si>
+  <si>
+    <t>JT9001641302438</t>
+  </si>
+  <si>
+    <t>JT5508128994068</t>
+  </si>
+  <si>
+    <t>79124720761631</t>
+  </si>
+  <si>
+    <t>465524045398552</t>
+  </si>
+  <si>
+    <t>YT8889268039280</t>
+  </si>
+  <si>
+    <t>79125229098775</t>
+  </si>
+  <si>
+    <t>777429621467758</t>
+  </si>
+  <si>
+    <t>25.07.26</t>
   </si>
 </sst>
 </file>
@@ -490,16 +310,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1022,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -1042,17 +856,17 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1062,7 +876,7 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1077,17 +891,17 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1097,7 +911,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1142,193 +956,193 @@
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="3" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="2" t="s">
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="3" t="s">
+    <row r="31" spans="1:1">
+      <c r="A31" s="3" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="2" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" s="2" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="3" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="2" t="s">
+    <row r="40" spans="1:1">
+      <c r="A40" s="3" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:1">
+      <c r="A43" s="2" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="2" t="s">
+    <row r="50" spans="1:1">
+      <c r="A50" s="3" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="3" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="3" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -1337,7 +1151,7 @@
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="2" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1357,17 +1171,17 @@
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="2" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1377,17 +1191,17 @@
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="2" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1402,323 +1216,28 @@
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2" t="s">
-        <v>75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
-      <c r="B77" t="s">
-        <v>137</v>
-      </c>
-    </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="5" t="s">
+      <c r="B78" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="B137" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="96">
   <si>
     <t>Track</t>
   </si>
@@ -27,236 +27,290 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>JT5508212661410</t>
-  </si>
-  <si>
-    <t>777429842412690</t>
-  </si>
-  <si>
-    <t>777429216776497</t>
-  </si>
-  <si>
-    <t>465527713805051</t>
-  </si>
-  <si>
-    <t>9818121142515</t>
-  </si>
-  <si>
-    <t>777429406871740</t>
-  </si>
-  <si>
-    <t>777429175898829</t>
-  </si>
-  <si>
-    <t>JT5508278682151</t>
-  </si>
-  <si>
-    <t>465525642438113</t>
-  </si>
-  <si>
-    <t>465528491327470</t>
-  </si>
-  <si>
-    <t>79124536639689</t>
-  </si>
-  <si>
-    <t>YT7634474645487</t>
-  </si>
-  <si>
-    <t>465528254213738</t>
-  </si>
-  <si>
-    <t>465524046250201</t>
-  </si>
-  <si>
-    <t>465528779706963</t>
-  </si>
-  <si>
-    <t>YT8889322954843</t>
-  </si>
-  <si>
-    <t>79124611305565</t>
-  </si>
-  <si>
-    <t>9818236349539</t>
-  </si>
-  <si>
-    <t>79124738593105</t>
-  </si>
-  <si>
-    <t>777429467409312</t>
-  </si>
-  <si>
-    <t>9818166888707</t>
-  </si>
-  <si>
-    <t>79124657949875</t>
-  </si>
-  <si>
-    <t>YT8889372438379</t>
-  </si>
-  <si>
-    <t>JT5508296019212</t>
-  </si>
-  <si>
-    <t>777429819921790</t>
-  </si>
-  <si>
-    <t>79124876732546</t>
-  </si>
-  <si>
-    <t>465526808457050</t>
-  </si>
-  <si>
-    <t>JT5508200550058</t>
-  </si>
-  <si>
-    <t>773433001136488</t>
-  </si>
-  <si>
-    <t>79124505797992</t>
-  </si>
-  <si>
-    <t>9818231853474</t>
-  </si>
-  <si>
-    <t>777429446345891</t>
-  </si>
-  <si>
-    <t>9818246238899</t>
-  </si>
-  <si>
-    <t>JT5508369197851</t>
-  </si>
-  <si>
-    <t>JT5508021872511</t>
-  </si>
-  <si>
-    <t>YT8890208690481</t>
-  </si>
-  <si>
-    <t>79124534861049</t>
-  </si>
-  <si>
-    <t>9818240933564</t>
-  </si>
-  <si>
-    <t>9818231641268</t>
-  </si>
-  <si>
-    <t>9818159442943</t>
-  </si>
-  <si>
-    <t>JT5507816648203</t>
-  </si>
-  <si>
-    <t>465536022619845</t>
-  </si>
-  <si>
-    <t>JT5508405117992</t>
-  </si>
-  <si>
-    <t>YT8889680544962</t>
-  </si>
-  <si>
-    <t>YT8889503886464</t>
-  </si>
-  <si>
-    <t>465535089190368</t>
-  </si>
-  <si>
-    <t>777428987726191</t>
-  </si>
-  <si>
-    <t>777429575873017</t>
-  </si>
-  <si>
-    <t>YT8888878763433</t>
-  </si>
-  <si>
-    <t>777429552673225</t>
-  </si>
-  <si>
-    <t>465525714739882</t>
-  </si>
-  <si>
-    <t>777429440275991</t>
-  </si>
-  <si>
-    <t>777429534217342</t>
-  </si>
-  <si>
-    <t>79125116358608</t>
-  </si>
-  <si>
-    <t>YT8888617717493</t>
-  </si>
-  <si>
-    <t>79125215678036</t>
-  </si>
-  <si>
-    <t>79125103299073</t>
-  </si>
-  <si>
-    <t>465523384478124</t>
-  </si>
-  <si>
-    <t>YT8889407297212</t>
-  </si>
-  <si>
-    <t>465523583671035</t>
-  </si>
-  <si>
-    <t>YT8889363892571</t>
-  </si>
-  <si>
-    <t>777429615568237</t>
-  </si>
-  <si>
-    <t>777430158147321</t>
-  </si>
-  <si>
-    <t>JT5508106864897</t>
-  </si>
-  <si>
-    <t>JT5508317923472</t>
-  </si>
-  <si>
-    <t>777429764323295</t>
-  </si>
-  <si>
-    <t>8218216547421</t>
-  </si>
-  <si>
-    <t>JT9001641302438</t>
-  </si>
-  <si>
-    <t>JT5508128994068</t>
-  </si>
-  <si>
-    <t>79124720761631</t>
-  </si>
-  <si>
-    <t>465524045398552</t>
-  </si>
-  <si>
-    <t>YT8889268039280</t>
-  </si>
-  <si>
-    <t>79125229098775</t>
-  </si>
-  <si>
-    <t>777429621467758</t>
-  </si>
-  <si>
     <t>25.07.26</t>
+  </si>
+  <si>
+    <t>YT8891897134557</t>
+  </si>
+  <si>
+    <t>777432092100584</t>
+  </si>
+  <si>
+    <t>79127010733647</t>
+  </si>
+  <si>
+    <t>79126562788491</t>
+  </si>
+  <si>
+    <t>79022353735996</t>
+  </si>
+  <si>
+    <t>79126995864544</t>
+  </si>
+  <si>
+    <t>79125661408398</t>
+  </si>
+  <si>
+    <t>79126896512999</t>
+  </si>
+  <si>
+    <t>79126657805236</t>
+  </si>
+  <si>
+    <t>79125662919124</t>
+  </si>
+  <si>
+    <t>79126824946485</t>
+  </si>
+  <si>
+    <t>9818382806860</t>
+  </si>
+  <si>
+    <t>79126700521951</t>
+  </si>
+  <si>
+    <t>465546553155218</t>
+  </si>
+  <si>
+    <t>777431127882333</t>
+  </si>
+  <si>
+    <t>9818357476853</t>
+  </si>
+  <si>
+    <t>777432125697657</t>
+  </si>
+  <si>
+    <t>9818385955633</t>
+  </si>
+  <si>
+    <t>79126665761106</t>
+  </si>
+  <si>
+    <t>9818355457295</t>
+  </si>
+  <si>
+    <t>79126334420888</t>
+  </si>
+  <si>
+    <t>9818345684947</t>
+  </si>
+  <si>
+    <t>9818368763844</t>
+  </si>
+  <si>
+    <t>79126709533161</t>
+  </si>
+  <si>
+    <t>79126250681329</t>
+  </si>
+  <si>
+    <t>9818387986149</t>
+  </si>
+  <si>
+    <t>79126622450624</t>
+  </si>
+  <si>
+    <t>9818341208609</t>
+  </si>
+  <si>
+    <t>9818382717349</t>
+  </si>
+  <si>
+    <t>9818326022938</t>
+  </si>
+  <si>
+    <t>79126625094930</t>
+  </si>
+  <si>
+    <t>79126562991215</t>
+  </si>
+  <si>
+    <t>YT8891909119176</t>
+  </si>
+  <si>
+    <t>9818336689278</t>
+  </si>
+  <si>
+    <t>79126384928607</t>
+  </si>
+  <si>
+    <t>79126201907033</t>
+  </si>
+  <si>
+    <t>9818380085725</t>
+  </si>
+  <si>
+    <t>465543566777196</t>
+  </si>
+  <si>
+    <t>9818377794315</t>
+  </si>
+  <si>
+    <t>79126606315278</t>
+  </si>
+  <si>
+    <t>777432167222781</t>
+  </si>
+  <si>
+    <t>9818373142201</t>
+  </si>
+  <si>
+    <t>9818447906456</t>
+  </si>
+  <si>
+    <t>79020619222184</t>
+  </si>
+  <si>
+    <t>79126520553614</t>
+  </si>
+  <si>
+    <t>79126478668925</t>
+  </si>
+  <si>
+    <t>79124757791321</t>
+  </si>
+  <si>
+    <t>YT8891831940365</t>
+  </si>
+  <si>
+    <t>777431385521296</t>
+  </si>
+  <si>
+    <t>465549582038706</t>
+  </si>
+  <si>
+    <t>777430868980561</t>
+  </si>
+  <si>
+    <t>465547146132090</t>
+  </si>
+  <si>
+    <t>YT8891506440392</t>
+  </si>
+  <si>
+    <t>9818383563980</t>
+  </si>
+  <si>
+    <t>79126749253511</t>
+  </si>
+  <si>
+    <t>9818361400289</t>
+  </si>
+  <si>
+    <t>777431960209962</t>
+  </si>
+  <si>
+    <t>JT5510597159096</t>
+  </si>
+  <si>
+    <t>465548264826153</t>
+  </si>
+  <si>
+    <t>JT5511184366216</t>
+  </si>
+  <si>
+    <t>YT8891580846420</t>
+  </si>
+  <si>
+    <t>465546740549273</t>
+  </si>
+  <si>
+    <t>777430920982555</t>
+  </si>
+  <si>
+    <t>YT8891795116590</t>
+  </si>
+  <si>
+    <t>JT5510135579978</t>
+  </si>
+  <si>
+    <t>YT8891278714105</t>
+  </si>
+  <si>
+    <t>YT8891881900904</t>
+  </si>
+  <si>
+    <t>777432088183502</t>
+  </si>
+  <si>
+    <t>79126284650210</t>
+  </si>
+  <si>
+    <t>9818446077705</t>
+  </si>
+  <si>
+    <t>777432059013391</t>
+  </si>
+  <si>
+    <t>777430903351626</t>
+  </si>
+  <si>
+    <t>YT8891767150454</t>
+  </si>
+  <si>
+    <t>YT8890992018243</t>
+  </si>
+  <si>
+    <t>9818387096840</t>
+  </si>
+  <si>
+    <t>JT5510649920333</t>
+  </si>
+  <si>
+    <t>YT8891880478978</t>
+  </si>
+  <si>
+    <t>JT5510140227778</t>
+  </si>
+  <si>
+    <t>9818387087110</t>
+  </si>
+  <si>
+    <t>JT5510061906537</t>
+  </si>
+  <si>
+    <t>777432158518297</t>
+  </si>
+  <si>
+    <t>JT5510132982176</t>
+  </si>
+  <si>
+    <t>465549042589756</t>
+  </si>
+  <si>
+    <t>YT8891325773525</t>
+  </si>
+  <si>
+    <t>465548552468967</t>
+  </si>
+  <si>
+    <t>JT5510355734148</t>
+  </si>
+  <si>
+    <t>777432063211602</t>
+  </si>
+  <si>
+    <t>465548548886001</t>
+  </si>
+  <si>
+    <t>JT5511185882148</t>
+  </si>
+  <si>
+    <t>465549081115766</t>
+  </si>
+  <si>
+    <t>9818442599394</t>
+  </si>
+  <si>
+    <t>01.08.26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,7 +322,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -304,8 +358,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
@@ -315,16 +372,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" quotePrefix="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="2"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -836,15 +894,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D78"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:D171"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" customWidth="1"/>
     <col min="4" max="4" width="23.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -855,389 +913,474 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="3" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="3" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="3" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="2" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="3" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="3" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="3" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="3" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="3" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="3" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="2" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="2" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="3" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="3" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="3" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="2" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="3" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="3" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="3" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="3" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="3" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="2" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="2" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="2" t="s">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="3" t="s">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="3" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="3" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="3" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="2" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="3" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="2" t="s">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="2" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="2" t="s">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="3" t="s">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="3" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="3" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="2" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="3" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="3" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="3" t="s">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="3" t="s">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="3" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="2" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="3" t="s">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="3" t="s">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="3" t="s">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="2" t="s">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="3" t="s">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="2" t="s">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="3" t="s">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="3" t="s">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="2" t="s">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="2" t="s">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="3" t="s">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="3" t="s">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="2" t="s">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="2" t="s">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="3" t="s">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="3" t="s">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="2" t="s">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="3" t="s">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="3" t="s">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
-      <c r="B78" t="s">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B171" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1249,7 +1392,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1258,7 +1401,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
   <si>
     <t>Track</t>
   </si>
@@ -30,287 +30,329 @@
     <t>25.07.26</t>
   </si>
   <si>
-    <t>YT8891897134557</t>
-  </si>
-  <si>
-    <t>777432092100584</t>
-  </si>
-  <si>
-    <t>79127010733647</t>
-  </si>
-  <si>
-    <t>79126562788491</t>
-  </si>
-  <si>
-    <t>79022353735996</t>
-  </si>
-  <si>
-    <t>79126995864544</t>
-  </si>
-  <si>
-    <t>79125661408398</t>
-  </si>
-  <si>
-    <t>79126896512999</t>
-  </si>
-  <si>
-    <t>79126657805236</t>
-  </si>
-  <si>
-    <t>79125662919124</t>
-  </si>
-  <si>
-    <t>79126824946485</t>
-  </si>
-  <si>
-    <t>9818382806860</t>
-  </si>
-  <si>
-    <t>79126700521951</t>
-  </si>
-  <si>
-    <t>465546553155218</t>
-  </si>
-  <si>
-    <t>777431127882333</t>
-  </si>
-  <si>
-    <t>9818357476853</t>
-  </si>
-  <si>
-    <t>777432125697657</t>
-  </si>
-  <si>
-    <t>9818385955633</t>
-  </si>
-  <si>
-    <t>79126665761106</t>
-  </si>
-  <si>
-    <t>9818355457295</t>
-  </si>
-  <si>
-    <t>79126334420888</t>
-  </si>
-  <si>
-    <t>9818345684947</t>
-  </si>
-  <si>
-    <t>9818368763844</t>
-  </si>
-  <si>
-    <t>79126709533161</t>
-  </si>
-  <si>
-    <t>79126250681329</t>
-  </si>
-  <si>
-    <t>9818387986149</t>
-  </si>
-  <si>
-    <t>79126622450624</t>
-  </si>
-  <si>
-    <t>9818341208609</t>
-  </si>
-  <si>
-    <t>9818382717349</t>
-  </si>
-  <si>
-    <t>9818326022938</t>
-  </si>
-  <si>
-    <t>79126625094930</t>
-  </si>
-  <si>
-    <t>79126562991215</t>
-  </si>
-  <si>
-    <t>YT8891909119176</t>
-  </si>
-  <si>
-    <t>9818336689278</t>
-  </si>
-  <si>
-    <t>79126384928607</t>
-  </si>
-  <si>
-    <t>79126201907033</t>
-  </si>
-  <si>
-    <t>9818380085725</t>
-  </si>
-  <si>
-    <t>465543566777196</t>
-  </si>
-  <si>
-    <t>9818377794315</t>
-  </si>
-  <si>
-    <t>79126606315278</t>
-  </si>
-  <si>
-    <t>777432167222781</t>
-  </si>
-  <si>
-    <t>9818373142201</t>
-  </si>
-  <si>
-    <t>9818447906456</t>
-  </si>
-  <si>
-    <t>79020619222184</t>
-  </si>
-  <si>
-    <t>79126520553614</t>
-  </si>
-  <si>
-    <t>79126478668925</t>
-  </si>
-  <si>
-    <t>79124757791321</t>
-  </si>
-  <si>
-    <t>YT8891831940365</t>
-  </si>
-  <si>
-    <t>777431385521296</t>
-  </si>
-  <si>
-    <t>465549582038706</t>
-  </si>
-  <si>
-    <t>777430868980561</t>
-  </si>
-  <si>
-    <t>465547146132090</t>
-  </si>
-  <si>
-    <t>YT8891506440392</t>
-  </si>
-  <si>
-    <t>9818383563980</t>
-  </si>
-  <si>
-    <t>79126749253511</t>
-  </si>
-  <si>
-    <t>9818361400289</t>
-  </si>
-  <si>
-    <t>777431960209962</t>
-  </si>
-  <si>
-    <t>JT5510597159096</t>
-  </si>
-  <si>
-    <t>465548264826153</t>
-  </si>
-  <si>
-    <t>JT5511184366216</t>
-  </si>
-  <si>
-    <t>YT8891580846420</t>
-  </si>
-  <si>
-    <t>465546740549273</t>
-  </si>
-  <si>
-    <t>777430920982555</t>
-  </si>
-  <si>
-    <t>YT8891795116590</t>
-  </si>
-  <si>
-    <t>JT5510135579978</t>
-  </si>
-  <si>
-    <t>YT8891278714105</t>
-  </si>
-  <si>
-    <t>YT8891881900904</t>
-  </si>
-  <si>
-    <t>777432088183502</t>
-  </si>
-  <si>
-    <t>79126284650210</t>
-  </si>
-  <si>
-    <t>9818446077705</t>
-  </si>
-  <si>
-    <t>777432059013391</t>
-  </si>
-  <si>
-    <t>777430903351626</t>
-  </si>
-  <si>
-    <t>YT8891767150454</t>
-  </si>
-  <si>
-    <t>YT8890992018243</t>
-  </si>
-  <si>
-    <t>9818387096840</t>
-  </si>
-  <si>
-    <t>JT5510649920333</t>
-  </si>
-  <si>
-    <t>YT8891880478978</t>
-  </si>
-  <si>
-    <t>JT5510140227778</t>
-  </si>
-  <si>
-    <t>9818387087110</t>
-  </si>
-  <si>
-    <t>JT5510061906537</t>
-  </si>
-  <si>
-    <t>777432158518297</t>
-  </si>
-  <si>
-    <t>JT5510132982176</t>
-  </si>
-  <si>
-    <t>465549042589756</t>
-  </si>
-  <si>
-    <t>YT8891325773525</t>
-  </si>
-  <si>
-    <t>465548552468967</t>
-  </si>
-  <si>
-    <t>JT5510355734148</t>
-  </si>
-  <si>
-    <t>777432063211602</t>
-  </si>
-  <si>
-    <t>465548548886001</t>
-  </si>
-  <si>
-    <t>JT5511185882148</t>
-  </si>
-  <si>
-    <t>465549081115766</t>
-  </si>
-  <si>
-    <t>9818442599394</t>
-  </si>
-  <si>
     <t>01.08.26</t>
+  </si>
+  <si>
+    <t>9818450184231</t>
+  </si>
+  <si>
+    <t>9818426166013</t>
+  </si>
+  <si>
+    <t>9818416320957</t>
+  </si>
+  <si>
+    <t>9818433028514</t>
+  </si>
+  <si>
+    <t>9818432239211</t>
+  </si>
+  <si>
+    <t>777431524968598</t>
+  </si>
+  <si>
+    <t>YT0700518262440</t>
+  </si>
+  <si>
+    <t>465546388169093</t>
+  </si>
+  <si>
+    <t>777431814676152</t>
+  </si>
+  <si>
+    <t>JT5510837895468</t>
+  </si>
+  <si>
+    <t>79127242186705</t>
+  </si>
+  <si>
+    <t>79127373920363</t>
+  </si>
+  <si>
+    <t>9818438782958</t>
+  </si>
+  <si>
+    <t>9818417331121</t>
+  </si>
+  <si>
+    <t>79127374839900</t>
+  </si>
+  <si>
+    <t>465544911613463</t>
+  </si>
+  <si>
+    <t>777431570968547</t>
+  </si>
+  <si>
+    <t>JT5510801329416</t>
+  </si>
+  <si>
+    <t>777432306666385</t>
+  </si>
+  <si>
+    <t>777431799572907</t>
+  </si>
+  <si>
+    <t>JT5511348950810</t>
+  </si>
+  <si>
+    <t>YT8891252142287</t>
+  </si>
+  <si>
+    <t>465556019742400</t>
+  </si>
+  <si>
+    <t>JT5510911553812</t>
+  </si>
+  <si>
+    <t>YT0700293528005</t>
+  </si>
+  <si>
+    <t>YT0700309231758</t>
+  </si>
+  <si>
+    <t>JT5511079208860</t>
+  </si>
+  <si>
+    <t>465556047304506</t>
+  </si>
+  <si>
+    <t>79127624645207</t>
+  </si>
+  <si>
+    <t>777431487924690</t>
+  </si>
+  <si>
+    <t>465537207856745</t>
+  </si>
+  <si>
+    <t>JT5509609406847</t>
+  </si>
+  <si>
+    <t>YT8891455596573</t>
+  </si>
+  <si>
+    <t>JT5509608475074</t>
+  </si>
+  <si>
+    <t>465544797721518</t>
+  </si>
+  <si>
+    <t>777431782575564</t>
+  </si>
+  <si>
+    <t>465540793246851</t>
+  </si>
+  <si>
+    <t>JT5511318942059</t>
+  </si>
+  <si>
+    <t>777431718343036</t>
+  </si>
+  <si>
+    <t>JT0024961812748</t>
+  </si>
+  <si>
+    <t>465540764130879</t>
+  </si>
+  <si>
+    <t>JT5509468347170</t>
+  </si>
+  <si>
+    <t>JT9001615602371</t>
+  </si>
+  <si>
+    <t>777430990907385</t>
+  </si>
+  <si>
+    <t>465554416503385</t>
+  </si>
+  <si>
+    <t>JT5510929162370</t>
+  </si>
+  <si>
+    <t>JT5510758460669</t>
+  </si>
+  <si>
+    <t>YT8890469266184</t>
+  </si>
+  <si>
+    <t>YT0700585927071</t>
+  </si>
+  <si>
+    <t>465544940962325</t>
+  </si>
+  <si>
+    <t>777431822047197</t>
+  </si>
+  <si>
+    <t>YT8891725701106</t>
+  </si>
+  <si>
+    <t>YT8891041223746</t>
+  </si>
+  <si>
+    <t>JT9002569718612</t>
+  </si>
+  <si>
+    <t>9818414148842</t>
+  </si>
+  <si>
+    <t>9818435120077</t>
+  </si>
+  <si>
+    <t>79022772227922</t>
+  </si>
+  <si>
+    <t>777431391225491</t>
+  </si>
+  <si>
+    <t>JT5509366926889</t>
+  </si>
+  <si>
+    <t>YT8891093205709</t>
+  </si>
+  <si>
+    <t>JT5511321106782</t>
+  </si>
+  <si>
+    <t>YT8891243993171</t>
+  </si>
+  <si>
+    <t>465554416482432</t>
+  </si>
+  <si>
+    <t>YT8891192685446</t>
+  </si>
+  <si>
+    <t>777431213310336</t>
+  </si>
+  <si>
+    <t>777431402453413</t>
+  </si>
+  <si>
+    <t>777431866529389</t>
+  </si>
+  <si>
+    <t>465548506828718</t>
+  </si>
+  <si>
+    <t>YT8890610932335</t>
+  </si>
+  <si>
+    <t>JT5510320544977</t>
+  </si>
+  <si>
+    <t>773433959430712</t>
+  </si>
+  <si>
+    <t>465552811561318</t>
+  </si>
+  <si>
+    <t>777431755182224</t>
+  </si>
+  <si>
+    <t>777431926783910</t>
+  </si>
+  <si>
+    <t>JT5511310534500</t>
+  </si>
+  <si>
+    <t>465548555037116</t>
+  </si>
+  <si>
+    <t>777431725933494</t>
+  </si>
+  <si>
+    <t>465543915154973</t>
+  </si>
+  <si>
+    <t>465549116389926</t>
+  </si>
+  <si>
+    <t>777430590274399</t>
+  </si>
+  <si>
+    <t>777431116584827</t>
+  </si>
+  <si>
+    <t>JT5510305927828</t>
+  </si>
+  <si>
+    <t>JT5510297714832</t>
+  </si>
+  <si>
+    <t>465543771658704</t>
+  </si>
+  <si>
+    <t>777431124200654</t>
+  </si>
+  <si>
+    <t>465552674163355</t>
+  </si>
+  <si>
+    <t>777431256875689</t>
+  </si>
+  <si>
+    <t>JT5509646192591</t>
+  </si>
+  <si>
+    <t>465543196516776</t>
+  </si>
+  <si>
+    <t>777430895443945</t>
+  </si>
+  <si>
+    <t>465549583281127</t>
+  </si>
+  <si>
+    <t>YT8891307709069</t>
+  </si>
+  <si>
+    <t>465540471534054</t>
+  </si>
+  <si>
+    <t>YT8890966073847</t>
+  </si>
+  <si>
+    <t>YT8890963162173</t>
+  </si>
+  <si>
+    <t>YT8891572988295</t>
+  </si>
+  <si>
+    <t>79127642102924</t>
+  </si>
+  <si>
+    <t>79127471184534</t>
+  </si>
+  <si>
+    <t>79127494002249</t>
+  </si>
+  <si>
+    <t>79127154318589</t>
+  </si>
+  <si>
+    <t>JT5510567192658</t>
+  </si>
+  <si>
+    <t>S71852393329001</t>
+  </si>
+  <si>
+    <t>465544381997453</t>
+  </si>
+  <si>
+    <t>JT5510810136700</t>
+  </si>
+  <si>
+    <t>2.08.26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,6 +367,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -334,7 +383,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -342,28 +391,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -372,17 +409,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" quotePrefix="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
     <cellStyle name="Normal 3" xfId="2"/>
+    <cellStyle name="Normal 4" xfId="3"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -894,15 +932,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D171"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D278"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" customWidth="1"/>
     <col min="4" max="4" width="23.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -913,474 +951,549 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:2">
       <c r="B78" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+    <row r="171" spans="1:2">
+      <c r="B171" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
+    <row r="172" spans="1:2">
+      <c r="A172" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
+    <row r="173" spans="1:2">
+      <c r="A173" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
+    <row r="174" spans="1:2">
+      <c r="A174" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+    <row r="175" spans="1:2">
+      <c r="A175" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+    <row r="176" spans="1:2">
+      <c r="A176" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
+    <row r="177" spans="1:1">
+      <c r="A177" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
+    <row r="178" spans="1:1">
+      <c r="A178" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
+    <row r="179" spans="1:1">
+      <c r="A179" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
+    <row r="180" spans="1:1">
+      <c r="A180" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
+    <row r="181" spans="1:1">
+      <c r="A181" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
+    <row r="182" spans="1:1">
+      <c r="A182" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
+    <row r="183" spans="1:1">
+      <c r="A183" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
+    <row r="184" spans="1:1">
+      <c r="A184" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
+    <row r="185" spans="1:1">
+      <c r="A185" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
+    <row r="186" spans="1:1">
+      <c r="A186" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
+    <row r="187" spans="1:1">
+      <c r="A187" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
+    <row r="188" spans="1:1">
+      <c r="A188" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
+    <row r="189" spans="1:1">
+      <c r="A189" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
+    <row r="190" spans="1:1">
+      <c r="A190" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="3" t="s">
+    <row r="191" spans="1:1">
+      <c r="A191" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="3" t="s">
+    <row r="192" spans="1:1">
+      <c r="A192" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="3" t="s">
+    <row r="193" spans="1:1">
+      <c r="A193" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
+    <row r="194" spans="1:1">
+      <c r="A194" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
+    <row r="195" spans="1:1">
+      <c r="A195" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
+    <row r="196" spans="1:1">
+      <c r="A196" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
+    <row r="197" spans="1:1">
+      <c r="A197" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" s="3" t="s">
+    <row r="198" spans="1:1">
+      <c r="A198" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
+    <row r="199" spans="1:1">
+      <c r="A199" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" s="3" t="s">
+    <row r="200" spans="1:1">
+      <c r="A200" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" s="3" t="s">
+    <row r="201" spans="1:1">
+      <c r="A201" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" s="3" t="s">
+    <row r="202" spans="1:1">
+      <c r="A202" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
+    <row r="203" spans="1:1">
+      <c r="A203" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="3" t="s">
+    <row r="204" spans="1:1">
+      <c r="A204" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="3" t="s">
+    <row r="205" spans="1:1">
+      <c r="A205" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" s="3" t="s">
+    <row r="206" spans="1:1">
+      <c r="A206" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" s="3" t="s">
+    <row r="207" spans="1:1">
+      <c r="A207" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" s="3" t="s">
+    <row r="208" spans="1:1">
+      <c r="A208" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" s="3" t="s">
+    <row r="209" spans="1:1">
+      <c r="A209" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" s="3" t="s">
+    <row r="210" spans="1:1">
+      <c r="A210" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" s="3" t="s">
+    <row r="211" spans="1:1">
+      <c r="A211" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" s="3" t="s">
+    <row r="212" spans="1:1">
+      <c r="A212" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" s="3" t="s">
+    <row r="213" spans="1:1">
+      <c r="A213" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="3" t="s">
+    <row r="214" spans="1:1">
+      <c r="A214" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="3" t="s">
+    <row r="215" spans="1:1">
+      <c r="A215" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" s="3" t="s">
+    <row r="216" spans="1:1">
+      <c r="A216" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
+    <row r="217" spans="1:1">
+      <c r="A217" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
+    <row r="218" spans="1:1">
+      <c r="A218" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
+    <row r="219" spans="1:1">
+      <c r="A219" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A128" s="3" t="s">
+    <row r="220" spans="1:1">
+      <c r="A220" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
+    <row r="221" spans="1:1">
+      <c r="A221" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A130" s="3" t="s">
+    <row r="222" spans="1:1">
+      <c r="A222" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
+    <row r="223" spans="1:1">
+      <c r="A223" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
+    <row r="224" spans="1:1">
+      <c r="A224" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
+    <row r="225" spans="1:1">
+      <c r="A225" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A134" s="3" t="s">
+    <row r="226" spans="1:1">
+      <c r="A226" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A135" s="3" t="s">
+    <row r="227" spans="1:1">
+      <c r="A227" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A136" s="2" t="s">
+    <row r="228" spans="1:1">
+      <c r="A228" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" s="3" t="s">
+    <row r="229" spans="1:1">
+      <c r="A229" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" s="2" t="s">
+    <row r="230" spans="1:1">
+      <c r="A230" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
+    <row r="231" spans="1:1">
+      <c r="A231" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
+    <row r="232" spans="1:1">
+      <c r="A232" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" s="3" t="s">
+    <row r="233" spans="1:1">
+      <c r="A233" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" s="2" t="s">
+    <row r="234" spans="1:1">
+      <c r="A234" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" s="2" t="s">
+    <row r="235" spans="1:1">
+      <c r="A235" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" s="2" t="s">
+    <row r="236" spans="1:1">
+      <c r="A236" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A145" s="2" t="s">
+    <row r="237" spans="1:1">
+      <c r="A237" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A146" s="3" t="s">
+    <row r="238" spans="1:1">
+      <c r="A238" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
+    <row r="239" spans="1:1">
+      <c r="A239" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A148" s="3" t="s">
+    <row r="240" spans="1:1">
+      <c r="A240" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
+    <row r="241" spans="1:1">
+      <c r="A241" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
+    <row r="242" spans="1:1">
+      <c r="A242" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A152" s="2" t="s">
+    <row r="243" spans="1:1">
+      <c r="A243" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A153" s="2" t="s">
+    <row r="244" spans="1:1">
+      <c r="A244" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A154" s="3" t="s">
+    <row r="245" spans="1:1">
+      <c r="A245" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A155" s="2" t="s">
+    <row r="246" spans="1:1">
+      <c r="A246" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
+    <row r="247" spans="1:1">
+      <c r="A247" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A157" s="2" t="s">
+    <row r="248" spans="1:1">
+      <c r="A248" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A158" s="3" t="s">
+    <row r="249" spans="1:1">
+      <c r="A249" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A159" s="2" t="s">
+    <row r="250" spans="1:1">
+      <c r="A250" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A160" s="3" t="s">
+    <row r="251" spans="1:1">
+      <c r="A251" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A161" s="2" t="s">
+    <row r="252" spans="1:1">
+      <c r="A252" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
+    <row r="253" spans="1:1">
+      <c r="A253" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163" s="2" t="s">
+    <row r="254" spans="1:1">
+      <c r="A254" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="3" t="s">
+    <row r="255" spans="1:1">
+      <c r="A255" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A165" s="2" t="s">
+    <row r="256" spans="1:1">
+      <c r="A256" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A166" s="3" t="s">
+    <row r="257" spans="1:1">
+      <c r="A257" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A167" s="3" t="s">
+    <row r="258" spans="1:1">
+      <c r="A258" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" s="2" t="s">
+    <row r="259" spans="1:1">
+      <c r="A259" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="3" t="s">
+    <row r="260" spans="1:1">
+      <c r="A260" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="3" t="s">
+    <row r="261" spans="1:1">
+      <c r="A261" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B171" t="s">
+    <row r="262" spans="1:1">
+      <c r="A262" s="3" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="B278" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1392,7 +1505,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1401,7 +1514,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="122">
   <si>
     <t>Track</t>
   </si>
@@ -30,293 +30,365 @@
     <t>2.08.26</t>
   </si>
   <si>
-    <t>465555652660380</t>
-  </si>
-  <si>
-    <t>777432378881342</t>
-  </si>
-  <si>
-    <t>777432481130011</t>
-  </si>
-  <si>
-    <t>313075838295836</t>
-  </si>
-  <si>
-    <t>465551248621930</t>
-  </si>
-  <si>
-    <t>YT0700560949247</t>
-  </si>
-  <si>
-    <t>777432470862713</t>
-  </si>
-  <si>
-    <t>YT0700033639613</t>
-  </si>
-  <si>
-    <t>JT5510702699570</t>
-  </si>
-  <si>
-    <t>JT5511973153680</t>
-  </si>
-  <si>
-    <t>YT7636081852193</t>
-  </si>
-  <si>
-    <t>JT5510917714135</t>
-  </si>
-  <si>
-    <t>YT0700649807824</t>
-  </si>
-  <si>
-    <t>JT5511912987930</t>
-  </si>
-  <si>
-    <t>777431648147834</t>
-  </si>
-  <si>
-    <t>777432250208460</t>
-  </si>
-  <si>
-    <t>YT0700560157226</t>
-  </si>
-  <si>
-    <t>777431660785017</t>
-  </si>
-  <si>
-    <t>777432270160105</t>
-  </si>
-  <si>
-    <t>777432221794253</t>
-  </si>
-  <si>
-    <t>777432408169779</t>
-  </si>
-  <si>
-    <t>777432184056112</t>
-  </si>
-  <si>
-    <t>YT0700577599440</t>
-  </si>
-  <si>
-    <t>777432391504005</t>
-  </si>
-  <si>
-    <t>JT5510914728341</t>
-  </si>
-  <si>
-    <t>465550137059361</t>
-  </si>
-  <si>
-    <t>YT0700368351174</t>
-  </si>
-  <si>
-    <t>YT8892362552036</t>
-  </si>
-  <si>
-    <t>YT0700117383700</t>
-  </si>
-  <si>
-    <t>465553583088242</t>
-  </si>
-  <si>
-    <t>YT0700369824068</t>
-  </si>
-  <si>
-    <t>777431676072240</t>
-  </si>
-  <si>
-    <t>777432477122243</t>
-  </si>
-  <si>
-    <t>777432663036500</t>
-  </si>
-  <si>
-    <t>JT5512024904547</t>
-  </si>
-  <si>
-    <t>JT5511891191583</t>
-  </si>
-  <si>
-    <t>777432466543501</t>
-  </si>
-  <si>
-    <t>777429492292130</t>
-  </si>
-  <si>
-    <t>465558765931389</t>
-  </si>
-  <si>
-    <t>465552096769480</t>
-  </si>
-  <si>
-    <t>YT8892560147218</t>
-  </si>
-  <si>
-    <t>YT0700020043612</t>
-  </si>
-  <si>
-    <t>465556047210629</t>
-  </si>
-  <si>
-    <t>JT5511735288630</t>
-  </si>
-  <si>
-    <t>777432355607831</t>
-  </si>
-  <si>
-    <t>777431653134158</t>
-  </si>
-  <si>
-    <t>JT5511729139154</t>
-  </si>
-  <si>
-    <t>465551614318475</t>
-  </si>
-  <si>
-    <t>777432680249682</t>
-  </si>
-  <si>
-    <t>777432285504366</t>
-  </si>
-  <si>
-    <t>YT8892362101364</t>
-  </si>
-  <si>
-    <t>JT5511748199726</t>
-  </si>
-  <si>
-    <t>JT5511907159189</t>
-  </si>
-  <si>
-    <t>777432446417598</t>
-  </si>
-  <si>
-    <t>YT8892426122009</t>
-  </si>
-  <si>
-    <t>773434720557336</t>
-  </si>
-  <si>
-    <t>465558694397552</t>
-  </si>
-  <si>
-    <t>YT0700597569647</t>
-  </si>
-  <si>
-    <t>YT0700616152270</t>
-  </si>
-  <si>
-    <t>JT5510881627338</t>
-  </si>
-  <si>
-    <t>313076959715943</t>
-  </si>
-  <si>
-    <t>777432658497305</t>
-  </si>
-  <si>
-    <t>79127714461538</t>
-  </si>
-  <si>
-    <t>777432185033186</t>
-  </si>
-  <si>
-    <t>465557629034254</t>
-  </si>
-  <si>
-    <t>465551743051717</t>
-  </si>
-  <si>
-    <t>YT8892186939080</t>
-  </si>
-  <si>
-    <t>JT5511728205740</t>
-  </si>
-  <si>
-    <t>465551842614031</t>
-  </si>
-  <si>
-    <t>JT5511907726353</t>
-  </si>
-  <si>
-    <t>465558592879946</t>
-  </si>
-  <si>
-    <t>YT0700336055592</t>
-  </si>
-  <si>
-    <t>465550458587016</t>
-  </si>
-  <si>
-    <t>777432246140664</t>
-  </si>
-  <si>
-    <t>777432263500258</t>
-  </si>
-  <si>
-    <t>465551470001808</t>
-  </si>
-  <si>
-    <t>465551581548192</t>
-  </si>
-  <si>
-    <t>YT8892595504448</t>
-  </si>
-  <si>
-    <t>772074120654568</t>
-  </si>
-  <si>
-    <t>465551672943085</t>
-  </si>
-  <si>
-    <t>777432240513929</t>
-  </si>
-  <si>
-    <t>JT5510762925121</t>
-  </si>
-  <si>
-    <t>777432214675708</t>
-  </si>
-  <si>
-    <t>JT5511973902656</t>
-  </si>
-  <si>
-    <t>777432279361848</t>
-  </si>
-  <si>
-    <t>777432678439867</t>
-  </si>
-  <si>
-    <t>YT8892351647709</t>
-  </si>
-  <si>
-    <t>465558909221993</t>
-  </si>
-  <si>
-    <t>YT8892361595988</t>
-  </si>
-  <si>
-    <t>YT0700600264066</t>
-  </si>
-  <si>
-    <t>JT5510949500563</t>
-  </si>
-  <si>
-    <t>465553370173853</t>
-  </si>
-  <si>
-    <t>JT5510751101070</t>
-  </si>
-  <si>
-    <t>JT5511973202283</t>
+    <t>777433273407183</t>
+  </si>
+  <si>
+    <t>79128270372760</t>
+  </si>
+  <si>
+    <t>777433322711834</t>
+  </si>
+  <si>
+    <t>JT5512094610444</t>
+  </si>
+  <si>
+    <t>YT8892040544045</t>
+  </si>
+  <si>
+    <t>JT5511468329074</t>
+  </si>
+  <si>
+    <t>79128374000926</t>
+  </si>
+  <si>
+    <t>777433232691532</t>
+  </si>
+  <si>
+    <t>9818547937330</t>
+  </si>
+  <si>
+    <t>9818552206521</t>
+  </si>
+  <si>
+    <t>9818503112387</t>
+  </si>
+  <si>
+    <t>9818498149529</t>
+  </si>
+  <si>
+    <t>9818500926767</t>
+  </si>
+  <si>
+    <t>YT8892076008834</t>
+  </si>
+  <si>
+    <t>777433254767765</t>
+  </si>
+  <si>
+    <t>465561154027248</t>
+  </si>
+  <si>
+    <t>777433285043498</t>
+  </si>
+  <si>
+    <t>JT5511473365729</t>
+  </si>
+  <si>
+    <t>9818541708680</t>
+  </si>
+  <si>
+    <t>777433366322584</t>
+  </si>
+  <si>
+    <t>YT8892061692578</t>
+  </si>
+  <si>
+    <t>YT8892031646385</t>
+  </si>
+  <si>
+    <t>JT5511473342211</t>
+  </si>
+  <si>
+    <t>9818509361625</t>
+  </si>
+  <si>
+    <t>JT5512283275294</t>
+  </si>
+  <si>
+    <t>465561829796313</t>
+  </si>
+  <si>
+    <t>465560886014405</t>
+  </si>
+  <si>
+    <t>9818401933155</t>
+  </si>
+  <si>
+    <t>9818518626458</t>
+  </si>
+  <si>
+    <t>9818519387763</t>
+  </si>
+  <si>
+    <t>9818493468243</t>
+  </si>
+  <si>
+    <t>YT8892289572405</t>
+  </si>
+  <si>
+    <t>777432910747814</t>
+  </si>
+  <si>
+    <t>JT5511734479041</t>
+  </si>
+  <si>
+    <t>777433124174991</t>
+  </si>
+  <si>
+    <t>465559931542882</t>
+  </si>
+  <si>
+    <t>JT5512064404272</t>
+  </si>
+  <si>
+    <t>777432339555147</t>
+  </si>
+  <si>
+    <t>465561740442525</t>
+  </si>
+  <si>
+    <t>JT5512243027034</t>
+  </si>
+  <si>
+    <t>YT8892141670263</t>
+  </si>
+  <si>
+    <t>9818510774863</t>
+  </si>
+  <si>
+    <t>9818508786084</t>
+  </si>
+  <si>
+    <t>79128417391097</t>
+  </si>
+  <si>
+    <t>9818520350635</t>
+  </si>
+  <si>
+    <t>9818456722382</t>
+  </si>
+  <si>
+    <t>465563220054375</t>
+  </si>
+  <si>
+    <t>YT0700688484442</t>
+  </si>
+  <si>
+    <t>JT5512452699521</t>
+  </si>
+  <si>
+    <t>79128418249089</t>
+  </si>
+  <si>
+    <t>YT8892465165427</t>
+  </si>
+  <si>
+    <t>JT5512126267927</t>
+  </si>
+  <si>
+    <t>777433515128493</t>
+  </si>
+  <si>
+    <t>JT5512192803844</t>
+  </si>
+  <si>
+    <t>9818513242234</t>
+  </si>
+  <si>
+    <t>YT8891976970704</t>
+  </si>
+  <si>
+    <t>YT0700914599797</t>
+  </si>
+  <si>
+    <t>JT5511559582403</t>
+  </si>
+  <si>
+    <t>777433337604975</t>
+  </si>
+  <si>
+    <t>79128398822856</t>
+  </si>
+  <si>
+    <t>465560415501210</t>
+  </si>
+  <si>
+    <t>777432768614293</t>
+  </si>
+  <si>
+    <t>YT8892026380805</t>
+  </si>
+  <si>
+    <t>JT5512179884293</t>
+  </si>
+  <si>
+    <t>465561694490299</t>
+  </si>
+  <si>
+    <t>JT5512482002781</t>
+  </si>
+  <si>
+    <t>JT5512218328102</t>
+  </si>
+  <si>
+    <t>JT5512112945946</t>
+  </si>
+  <si>
+    <t>777433248544845</t>
+  </si>
+  <si>
+    <t>777433451328337</t>
+  </si>
+  <si>
+    <t>465561612416190</t>
+  </si>
+  <si>
+    <t>79128537297350</t>
+  </si>
+  <si>
+    <t>79128390557341</t>
+  </si>
+  <si>
+    <t>YT7636314623433</t>
+  </si>
+  <si>
+    <t>YT8892153588338</t>
+  </si>
+  <si>
+    <t>465563411934782</t>
+  </si>
+  <si>
+    <t>9818554340255</t>
+  </si>
+  <si>
+    <t>JT5512072786519</t>
+  </si>
+  <si>
+    <t>777432202270866</t>
+  </si>
+  <si>
+    <t>YT8892114030067</t>
+  </si>
+  <si>
+    <t>YT8892262430414</t>
+  </si>
+  <si>
+    <t>465563237773688</t>
+  </si>
+  <si>
+    <t>777433254730510</t>
+  </si>
+  <si>
+    <t>YT8892072575086</t>
+  </si>
+  <si>
+    <t>JT5511588831500</t>
+  </si>
+  <si>
+    <t>777431892989855</t>
+  </si>
+  <si>
+    <t>465560379443127</t>
+  </si>
+  <si>
+    <t>79128587338705</t>
+  </si>
+  <si>
+    <t>777433411890371</t>
+  </si>
+  <si>
+    <t>YT8891975910578</t>
+  </si>
+  <si>
+    <t>YT8892044084761</t>
+  </si>
+  <si>
+    <t>465561440200257</t>
+  </si>
+  <si>
+    <t>JT5511806131274</t>
+  </si>
+  <si>
+    <t>JT5512121954745</t>
+  </si>
+  <si>
+    <t>79023224885096</t>
+  </si>
+  <si>
+    <t>465561768062743</t>
+  </si>
+  <si>
+    <t>777433041831948</t>
+  </si>
+  <si>
+    <t>JT5512622838370</t>
+  </si>
+  <si>
+    <t>773434980574008</t>
+  </si>
+  <si>
+    <t>465561773812215</t>
+  </si>
+  <si>
+    <t>9818496925657</t>
+  </si>
+  <si>
+    <t>JT5512519599078</t>
+  </si>
+  <si>
+    <t>777433308473725</t>
+  </si>
+  <si>
+    <t>JT5512074559494</t>
+  </si>
+  <si>
+    <t>YT0700725056359</t>
+  </si>
+  <si>
+    <t>465560306399303</t>
+  </si>
+  <si>
+    <t>JT5512158326398</t>
+  </si>
+  <si>
+    <t>465557921620292</t>
+  </si>
+  <si>
+    <t>YT8892036715488</t>
+  </si>
+  <si>
+    <t>JT5512080216494</t>
+  </si>
+  <si>
+    <t>9818495409530</t>
+  </si>
+  <si>
+    <t>YT8892153337178</t>
+  </si>
+  <si>
+    <t>79128211523486</t>
+  </si>
+  <si>
+    <t>79128643266809</t>
+  </si>
+  <si>
+    <t>JT5512622100092</t>
+  </si>
+  <si>
+    <t>DPK317149681895</t>
+  </si>
+  <si>
+    <t>06.08.26</t>
+  </si>
+  <si>
+    <t>JT5511621183806</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,6 +410,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -356,7 +435,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
@@ -370,25 +449,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" quotePrefix="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
     <cellStyle name="Normal 3" xfId="2"/>
     <cellStyle name="Normal 4" xfId="3"/>
     <cellStyle name="Normal 5" xfId="4"/>
+    <cellStyle name="Normal 6" xfId="5"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -901,14 +984,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D206"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" customWidth="1"/>
     <col min="4" max="4" width="23.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -919,492 +1002,607 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1">
       <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:1">
+      <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1">
       <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1">
       <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1">
       <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1">
       <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1">
       <c r="A31" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:1">
+      <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:1">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:1">
+      <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1">
       <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1">
       <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+    <row r="41" spans="1:1">
+      <c r="A41" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1">
       <c r="A42" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:1">
+      <c r="A43" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1">
       <c r="A47" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+    <row r="49" spans="1:1">
+      <c r="A49" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+    <row r="50" spans="1:1">
+      <c r="A50" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1">
       <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1">
       <c r="A53" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:1">
+      <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+    <row r="55" spans="1:1">
+      <c r="A55" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:1">
+      <c r="A56" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
+    <row r="57" spans="1:1">
+      <c r="A57" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
+    <row r="58" spans="1:1">
+      <c r="A58" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:1">
       <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+    <row r="60" spans="1:1">
+      <c r="A60" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+    <row r="61" spans="1:1">
+      <c r="A61" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1">
       <c r="A62" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:1">
       <c r="A63" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
+    <row r="64" spans="1:1">
+      <c r="A64" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+    <row r="65" spans="1:1">
+      <c r="A65" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1">
       <c r="A66" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+    <row r="67" spans="1:1">
+      <c r="A67" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1">
       <c r="A68" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1">
       <c r="A70" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+    <row r="71" spans="1:1">
+      <c r="A71" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:1">
       <c r="A72" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+    <row r="73" spans="1:1">
+      <c r="A73" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:1">
       <c r="A74" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
+    <row r="75" spans="1:1">
+      <c r="A75" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
+    <row r="76" spans="1:1">
+      <c r="A76" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:1">
       <c r="A77" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:1">
       <c r="A78" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:1">
       <c r="A79" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:1">
       <c r="A80" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
+    <row r="81" spans="1:1">
+      <c r="A81" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
+    <row r="82" spans="1:1">
+      <c r="A82" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+    <row r="83" spans="1:1">
+      <c r="A83" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:1">
       <c r="A84" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:1">
       <c r="A85" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
+    <row r="86" spans="1:1">
+      <c r="A86" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:1">
       <c r="A87" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
+    <row r="88" spans="1:1">
+      <c r="A88" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:1">
       <c r="A89" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
+    <row r="90" spans="1:1">
+      <c r="A90" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:1">
       <c r="A91" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:1">
       <c r="A92" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:1">
       <c r="A93" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:1">
       <c r="A94" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B98">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:1">
+      <c r="A96" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="1">
+        <v>465561139227964</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="B121" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2">
       <c r="B206" t="s">
         <v>3</v>
       </c>
@@ -1418,7 +1616,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1427,7 +1625,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="223">
   <si>
     <t>Track</t>
   </si>
@@ -27,9 +27,6 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>2.08.26</t>
-  </si>
-  <si>
     <t>777433273407183</t>
   </si>
   <si>
@@ -382,13 +379,319 @@
   </si>
   <si>
     <t>JT5511621183806</t>
+  </si>
+  <si>
+    <t>79127706270394</t>
+  </si>
+  <si>
+    <t>74100605564167</t>
+  </si>
+  <si>
+    <t>YT0700702001844</t>
+  </si>
+  <si>
+    <t>79128700370778</t>
+  </si>
+  <si>
+    <t>777433110454148</t>
+  </si>
+  <si>
+    <t>465569912598029</t>
+  </si>
+  <si>
+    <t>9818433282207</t>
+  </si>
+  <si>
+    <t>777433707106720</t>
+  </si>
+  <si>
+    <t>79128170695246</t>
+  </si>
+  <si>
+    <t>JT5512705072058</t>
+  </si>
+  <si>
+    <t>777433773600515</t>
+  </si>
+  <si>
+    <t>JT5512424325006</t>
+  </si>
+  <si>
+    <t>79128583028858</t>
+  </si>
+  <si>
+    <t>79127351089483</t>
+  </si>
+  <si>
+    <t>777433160869172</t>
+  </si>
+  <si>
+    <t>777433733368896</t>
+  </si>
+  <si>
+    <t>79128818782213</t>
+  </si>
+  <si>
+    <t>9818419775768</t>
+  </si>
+  <si>
+    <t>79127453643365</t>
+  </si>
+  <si>
+    <t>79128995056801</t>
+  </si>
+  <si>
+    <t>JT5512403451896</t>
+  </si>
+  <si>
+    <t>JT5512457436161</t>
+  </si>
+  <si>
+    <t>9818419208492</t>
+  </si>
+  <si>
+    <t>777432943900392</t>
+  </si>
+  <si>
+    <t>777433159318771</t>
+  </si>
+  <si>
+    <t>YT0700696692408</t>
+  </si>
+  <si>
+    <t>777433076760443</t>
+  </si>
+  <si>
+    <t>465569427223663</t>
+  </si>
+  <si>
+    <t>465567296650009</t>
+  </si>
+  <si>
+    <t>9818525784853</t>
+  </si>
+  <si>
+    <t>79128695560586</t>
+  </si>
+  <si>
+    <t>79128621006218</t>
+  </si>
+  <si>
+    <t>9818527301689</t>
+  </si>
+  <si>
+    <t>79129002974887</t>
+  </si>
+  <si>
+    <t>79128500985558</t>
+  </si>
+  <si>
+    <t>79129012268686</t>
+  </si>
+  <si>
+    <t>79128991753648</t>
+  </si>
+  <si>
+    <t>73720846946520</t>
+  </si>
+  <si>
+    <t>79128696577109</t>
+  </si>
+  <si>
+    <t>9818536471070</t>
+  </si>
+  <si>
+    <t>9818484581897</t>
+  </si>
+  <si>
+    <t>79128702033462</t>
+  </si>
+  <si>
+    <t>9818395534300</t>
+  </si>
+  <si>
+    <t>9818403665685</t>
+  </si>
+  <si>
+    <t>9818405361132</t>
+  </si>
+  <si>
+    <t>79128184916426</t>
+  </si>
+  <si>
+    <t>79127320165125</t>
+  </si>
+  <si>
+    <t>465565739154804</t>
+  </si>
+  <si>
+    <t>79127489707231</t>
+  </si>
+  <si>
+    <t>JT5512523311913</t>
+  </si>
+  <si>
+    <t>9818472600522</t>
+  </si>
+  <si>
+    <t>9818472493328</t>
+  </si>
+  <si>
+    <t>79128749780311</t>
+  </si>
+  <si>
+    <t>465570092501397</t>
+  </si>
+  <si>
+    <t>JT5512199856542</t>
+  </si>
+  <si>
+    <t>465568134459496</t>
+  </si>
+  <si>
+    <t>YT0701264749438</t>
+  </si>
+  <si>
+    <t>465569236100277</t>
+  </si>
+  <si>
+    <t>9818390234968</t>
+  </si>
+  <si>
+    <t>79127874375914</t>
+  </si>
+  <si>
+    <t>79127092793698</t>
+  </si>
+  <si>
+    <t>9818405244651</t>
+  </si>
+  <si>
+    <t>465565888422366</t>
+  </si>
+  <si>
+    <t>777433300602815</t>
+  </si>
+  <si>
+    <t>777432904258466</t>
+  </si>
+  <si>
+    <t>JT5512580795954</t>
+  </si>
+  <si>
+    <t>465569314373325</t>
+  </si>
+  <si>
+    <t>777432887257507</t>
+  </si>
+  <si>
+    <t>JT5512335764951</t>
+  </si>
+  <si>
+    <t>JT5512843409203</t>
+  </si>
+  <si>
+    <t>777433161035992</t>
+  </si>
+  <si>
+    <t>465559303847340</t>
+  </si>
+  <si>
+    <t>465568165162150</t>
+  </si>
+  <si>
+    <t>JT5512668956067</t>
+  </si>
+  <si>
+    <t>JT5512783930832</t>
+  </si>
+  <si>
+    <t>777432995133275</t>
+  </si>
+  <si>
+    <t>9818390375036</t>
+  </si>
+  <si>
+    <t>YT0700766452132</t>
+  </si>
+  <si>
+    <t>JT5512465786159</t>
+  </si>
+  <si>
+    <t>777433176347702</t>
+  </si>
+  <si>
+    <t>JT5512474750640</t>
+  </si>
+  <si>
+    <t>79127758477866</t>
+  </si>
+  <si>
+    <t>79127523572650</t>
+  </si>
+  <si>
+    <t>79128009266560</t>
+  </si>
+  <si>
+    <t>79127555673946</t>
+  </si>
+  <si>
+    <t>465562606004125</t>
+  </si>
+  <si>
+    <t>777433151565857</t>
+  </si>
+  <si>
+    <t>465565828239401</t>
+  </si>
+  <si>
+    <t>79127773900447</t>
+  </si>
+  <si>
+    <t>JT5512383999406</t>
+  </si>
+  <si>
+    <t>79129006950877</t>
+  </si>
+  <si>
+    <t>9818397686588</t>
+  </si>
+  <si>
+    <t>9818487709022</t>
+  </si>
+  <si>
+    <t>9818472832173</t>
+  </si>
+  <si>
+    <t>79128145186434</t>
+  </si>
+  <si>
+    <t>9818477035279</t>
+  </si>
+  <si>
+    <t>465566938430643</t>
+  </si>
+  <si>
+    <t>79128413790120</t>
+  </si>
+  <si>
+    <t>9818487715690</t>
+  </si>
+  <si>
+    <t>9818479375075</t>
+  </si>
+  <si>
+    <t>79128124832316</t>
+  </si>
+  <si>
+    <t>07.08.26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,7 +717,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -435,7 +738,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
@@ -452,8 +755,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -464,14 +770,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
     <cellStyle name="Normal 3" xfId="2"/>
     <cellStyle name="Normal 4" xfId="3"/>
     <cellStyle name="Normal 5" xfId="4"/>
     <cellStyle name="Normal 6" xfId="5"/>
+    <cellStyle name="Normal 7" xfId="6"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -983,15 +1296,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D206"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:D223"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" customWidth="1"/>
     <col min="4" max="4" width="23.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1002,609 +1315,1114 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="3" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="3" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="3" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="3" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="3" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="3" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="3" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="2" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="2" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="3" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="2" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="3" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="3" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="3" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="3" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="3" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="3" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="2" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="3" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="3" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="3" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="2" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="3" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="3" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="2" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="3" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="3" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="3" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="3" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="3" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="3" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="2" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="2" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="3" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="2" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="2" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="3" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="2" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="3" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="2" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="2" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="2" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="3" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="3" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="3" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="3" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="2" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="2" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="3" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="2" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="2" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="2" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="3" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="3" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="3" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="3" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="3" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="2" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="2" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="3" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="3" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="2" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="3" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="2" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="2" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="3" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="3" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="2" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="2" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="3" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="3" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="3" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="3" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="2" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="2" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="3" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="2" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="2" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="3" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="3" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="3" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="2" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="3" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="3" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="3" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="2" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="3" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="2" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="2" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="3" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="2" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="3" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="2" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="2" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="3" t="s">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="2" t="s">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="3" t="s">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="3" t="s">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="2" t="s">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>465561139227964</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B121" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
-      <c r="B121" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="206" spans="2:2">
-      <c r="B206" t="s">
-        <v>3</v>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B223" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -1616,7 +2434,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1625,7 +2443,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="98">
   <si>
     <t>Track</t>
   </si>
@@ -27,10 +27,289 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>06.08.26</t>
-  </si>
-  <si>
-    <t>07.08.26</t>
+    <t>JT0025066115699</t>
+  </si>
+  <si>
+    <t>777433856563195</t>
+  </si>
+  <si>
+    <t>777433739476901</t>
+  </si>
+  <si>
+    <t>YT0700887517882</t>
+  </si>
+  <si>
+    <t>YT0701314352454</t>
+  </si>
+  <si>
+    <t>777433841170338</t>
+  </si>
+  <si>
+    <t>465549252290332</t>
+  </si>
+  <si>
+    <t>465569411936239</t>
+  </si>
+  <si>
+    <t>777433671745217</t>
+  </si>
+  <si>
+    <t>701314495076</t>
+  </si>
+  <si>
+    <t>YT0700970389303</t>
+  </si>
+  <si>
+    <t>YT0701159825618</t>
+  </si>
+  <si>
+    <t>YT8893268926457</t>
+  </si>
+  <si>
+    <t>YT8893144142577</t>
+  </si>
+  <si>
+    <t>YT0701158861813</t>
+  </si>
+  <si>
+    <t>777434050976170</t>
+  </si>
+  <si>
+    <t>465567736767087</t>
+  </si>
+  <si>
+    <t>777433699389874</t>
+  </si>
+  <si>
+    <t>YT0701254688563</t>
+  </si>
+  <si>
+    <t>777433732351786</t>
+  </si>
+  <si>
+    <t>JT5512929435504</t>
+  </si>
+  <si>
+    <t>9840056909746</t>
+  </si>
+  <si>
+    <t>YT0701238200936</t>
+  </si>
+  <si>
+    <t>9818562435993</t>
+  </si>
+  <si>
+    <t>777433007904358</t>
+  </si>
+  <si>
+    <t>YT0701023018171</t>
+  </si>
+  <si>
+    <t>465567207526059</t>
+  </si>
+  <si>
+    <t>465566169789464</t>
+  </si>
+  <si>
+    <t>777433786111597</t>
+  </si>
+  <si>
+    <t>YT0701245500313</t>
+  </si>
+  <si>
+    <t>9840050663402</t>
+  </si>
+  <si>
+    <t>YT0701214758048</t>
+  </si>
+  <si>
+    <t>9818552381440</t>
+  </si>
+  <si>
+    <t>465564043205290</t>
+  </si>
+  <si>
+    <t>79129038752092</t>
+  </si>
+  <si>
+    <t>YT8892827580624</t>
+  </si>
+  <si>
+    <t>YT0701283811255</t>
+  </si>
+  <si>
+    <t>JT5513237468484</t>
+  </si>
+  <si>
+    <t>JT5513193877406</t>
+  </si>
+  <si>
+    <t>9818561019674</t>
+  </si>
+  <si>
+    <t>JT5513675093398</t>
+  </si>
+  <si>
+    <t>79128814029756</t>
+  </si>
+  <si>
+    <t>79128857545559</t>
+  </si>
+  <si>
+    <t>79129230300670</t>
+  </si>
+  <si>
+    <t>777434090393020</t>
+  </si>
+  <si>
+    <t>YT0701294554686</t>
+  </si>
+  <si>
+    <t>777433711450355</t>
+  </si>
+  <si>
+    <t>465565875662049</t>
+  </si>
+  <si>
+    <t>777433874590537</t>
+  </si>
+  <si>
+    <t>JT5512724538526</t>
+  </si>
+  <si>
+    <t>465566321766962</t>
+  </si>
+  <si>
+    <t>79128826754930</t>
+  </si>
+  <si>
+    <t>465566995872448</t>
+  </si>
+  <si>
+    <t>JT5512664136523</t>
+  </si>
+  <si>
+    <t>9818581111963</t>
+  </si>
+  <si>
+    <t>9818584360819</t>
+  </si>
+  <si>
+    <t>79129230309146</t>
+  </si>
+  <si>
+    <t>79129141494256</t>
+  </si>
+  <si>
+    <t>79129205750236</t>
+  </si>
+  <si>
+    <t>79129222778231</t>
+  </si>
+  <si>
+    <t>9818530207013</t>
+  </si>
+  <si>
+    <t>9818586683596</t>
+  </si>
+  <si>
+    <t>YT8892979283930</t>
+  </si>
+  <si>
+    <t>9818561987580</t>
+  </si>
+  <si>
+    <t>JT5513626163572</t>
+  </si>
+  <si>
+    <t>YT8893257692341</t>
+  </si>
+  <si>
+    <t>JT9002655758778</t>
+  </si>
+  <si>
+    <t>YT8892994401272</t>
+  </si>
+  <si>
+    <t>79129044047956</t>
+  </si>
+  <si>
+    <t>465566406174921</t>
+  </si>
+  <si>
+    <t>465563664573725</t>
+  </si>
+  <si>
+    <t>465574634283285</t>
+  </si>
+  <si>
+    <t>777434050892814</t>
+  </si>
+  <si>
+    <t>465566092886770</t>
+  </si>
+  <si>
+    <t>YT7637058244955</t>
+  </si>
+  <si>
+    <t>79128853693826</t>
+  </si>
+  <si>
+    <t>79129156123281</t>
+  </si>
+  <si>
+    <t>JT5513707504339</t>
+  </si>
+  <si>
+    <t>YT7637068719807</t>
+  </si>
+  <si>
+    <t>777433527468973</t>
+  </si>
+  <si>
+    <t>SF5111574911471</t>
+  </si>
+  <si>
+    <t>9840038387928</t>
+  </si>
+  <si>
+    <t>79129179322763</t>
+  </si>
+  <si>
+    <t>9840060133744</t>
+  </si>
+  <si>
+    <t>9818577037004</t>
+  </si>
+  <si>
+    <t>465564992037113</t>
+  </si>
+  <si>
+    <t>9818576706061</t>
+  </si>
+  <si>
+    <t>79128460260058</t>
+  </si>
+  <si>
+    <t>9818578550531</t>
+  </si>
+  <si>
+    <t>777434073315054</t>
+  </si>
+  <si>
+    <t>YT8893094760881</t>
+  </si>
+  <si>
+    <t>9818559892636</t>
+  </si>
+  <si>
+    <t>777433662475158</t>
+  </si>
+  <si>
+    <t>JT5513045238314</t>
+  </si>
+  <si>
+    <t>09.08.26</t>
   </si>
 </sst>
 </file>
@@ -105,10 +384,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -630,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -649,14 +934,494 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B121" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B223" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B99" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/china.xlsx
+++ b/china.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Track</t>
   </si>
@@ -27,289 +27,94 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>JT0025066115699</t>
-  </si>
-  <si>
-    <t>777433856563195</t>
-  </si>
-  <si>
-    <t>777433739476901</t>
-  </si>
-  <si>
-    <t>YT0700887517882</t>
-  </si>
-  <si>
-    <t>YT0701314352454</t>
-  </si>
-  <si>
-    <t>777433841170338</t>
-  </si>
-  <si>
-    <t>465549252290332</t>
-  </si>
-  <si>
-    <t>465569411936239</t>
-  </si>
-  <si>
-    <t>777433671745217</t>
-  </si>
-  <si>
-    <t>701314495076</t>
-  </si>
-  <si>
-    <t>YT0700970389303</t>
-  </si>
-  <si>
-    <t>YT0701159825618</t>
-  </si>
-  <si>
-    <t>YT8893268926457</t>
-  </si>
-  <si>
-    <t>YT8893144142577</t>
-  </si>
-  <si>
-    <t>YT0701158861813</t>
-  </si>
-  <si>
-    <t>777434050976170</t>
-  </si>
-  <si>
-    <t>465567736767087</t>
-  </si>
-  <si>
-    <t>777433699389874</t>
-  </si>
-  <si>
-    <t>YT0701254688563</t>
-  </si>
-  <si>
-    <t>777433732351786</t>
-  </si>
-  <si>
-    <t>JT5512929435504</t>
-  </si>
-  <si>
-    <t>9840056909746</t>
-  </si>
-  <si>
-    <t>YT0701238200936</t>
-  </si>
-  <si>
-    <t>9818562435993</t>
-  </si>
-  <si>
-    <t>777433007904358</t>
-  </si>
-  <si>
-    <t>YT0701023018171</t>
-  </si>
-  <si>
-    <t>465567207526059</t>
-  </si>
-  <si>
-    <t>465566169789464</t>
-  </si>
-  <si>
-    <t>777433786111597</t>
-  </si>
-  <si>
-    <t>YT0701245500313</t>
-  </si>
-  <si>
-    <t>9840050663402</t>
-  </si>
-  <si>
-    <t>YT0701214758048</t>
-  </si>
-  <si>
-    <t>9818552381440</t>
-  </si>
-  <si>
-    <t>465564043205290</t>
-  </si>
-  <si>
-    <t>79129038752092</t>
-  </si>
-  <si>
-    <t>YT8892827580624</t>
-  </si>
-  <si>
-    <t>YT0701283811255</t>
-  </si>
-  <si>
-    <t>JT5513237468484</t>
-  </si>
-  <si>
-    <t>JT5513193877406</t>
-  </si>
-  <si>
-    <t>9818561019674</t>
-  </si>
-  <si>
-    <t>JT5513675093398</t>
-  </si>
-  <si>
-    <t>79128814029756</t>
-  </si>
-  <si>
-    <t>79128857545559</t>
-  </si>
-  <si>
-    <t>79129230300670</t>
-  </si>
-  <si>
-    <t>777434090393020</t>
-  </si>
-  <si>
-    <t>YT0701294554686</t>
-  </si>
-  <si>
-    <t>777433711450355</t>
-  </si>
-  <si>
-    <t>465565875662049</t>
-  </si>
-  <si>
-    <t>777433874590537</t>
-  </si>
-  <si>
-    <t>JT5512724538526</t>
-  </si>
-  <si>
-    <t>465566321766962</t>
-  </si>
-  <si>
-    <t>79128826754930</t>
-  </si>
-  <si>
-    <t>465566995872448</t>
-  </si>
-  <si>
-    <t>JT5512664136523</t>
-  </si>
-  <si>
-    <t>9818581111963</t>
-  </si>
-  <si>
-    <t>9818584360819</t>
-  </si>
-  <si>
-    <t>79129230309146</t>
-  </si>
-  <si>
-    <t>79129141494256</t>
-  </si>
-  <si>
-    <t>79129205750236</t>
-  </si>
-  <si>
-    <t>79129222778231</t>
-  </si>
-  <si>
-    <t>9818530207013</t>
-  </si>
-  <si>
-    <t>9818586683596</t>
-  </si>
-  <si>
-    <t>YT8892979283930</t>
-  </si>
-  <si>
-    <t>9818561987580</t>
-  </si>
-  <si>
-    <t>JT5513626163572</t>
-  </si>
-  <si>
-    <t>YT8893257692341</t>
-  </si>
-  <si>
-    <t>JT9002655758778</t>
-  </si>
-  <si>
-    <t>YT8892994401272</t>
-  </si>
-  <si>
-    <t>79129044047956</t>
-  </si>
-  <si>
-    <t>465566406174921</t>
-  </si>
-  <si>
-    <t>465563664573725</t>
-  </si>
-  <si>
-    <t>465574634283285</t>
-  </si>
-  <si>
-    <t>777434050892814</t>
-  </si>
-  <si>
-    <t>465566092886770</t>
-  </si>
-  <si>
-    <t>YT7637058244955</t>
-  </si>
-  <si>
-    <t>79128853693826</t>
-  </si>
-  <si>
-    <t>79129156123281</t>
-  </si>
-  <si>
-    <t>JT5513707504339</t>
-  </si>
-  <si>
-    <t>YT7637068719807</t>
-  </si>
-  <si>
-    <t>777433527468973</t>
-  </si>
-  <si>
-    <t>SF5111574911471</t>
-  </si>
-  <si>
-    <t>9840038387928</t>
-  </si>
-  <si>
-    <t>79129179322763</t>
-  </si>
-  <si>
-    <t>9840060133744</t>
-  </si>
-  <si>
-    <t>9818577037004</t>
-  </si>
-  <si>
-    <t>465564992037113</t>
-  </si>
-  <si>
-    <t>9818576706061</t>
-  </si>
-  <si>
-    <t>79128460260058</t>
-  </si>
-  <si>
-    <t>9818578550531</t>
-  </si>
-  <si>
-    <t>777434073315054</t>
-  </si>
-  <si>
-    <t>YT8893094760881</t>
-  </si>
-  <si>
-    <t>9818559892636</t>
-  </si>
-  <si>
-    <t>777433662475158</t>
-  </si>
-  <si>
-    <t>JT5513045238314</t>
-  </si>
-  <si>
-    <t>09.08.26</t>
+    <t>DPK317147298462</t>
+  </si>
+  <si>
+    <t>JT5514695832192</t>
+  </si>
+  <si>
+    <t>JT5514136170830</t>
+  </si>
+  <si>
+    <t>JT5513737705831</t>
+  </si>
+  <si>
+    <t>JT5514205469407</t>
+  </si>
+  <si>
+    <t>JT5514251573866</t>
+  </si>
+  <si>
+    <t>JT5514212072439</t>
+  </si>
+  <si>
+    <t>YT8893873599659</t>
+  </si>
+  <si>
+    <t>YT8893640396748</t>
+  </si>
+  <si>
+    <t>JT5513724742314</t>
+  </si>
+  <si>
+    <t>YT8893564258412</t>
+  </si>
+  <si>
+    <t>YT0701917026688</t>
+  </si>
+  <si>
+    <t>JT5514432508668</t>
+  </si>
+  <si>
+    <t>JT5514476194551</t>
+  </si>
+  <si>
+    <t>JT5514530389324</t>
+  </si>
+  <si>
+    <t>YT8893729572461</t>
+  </si>
+  <si>
+    <t>JT5513851297687</t>
+  </si>
+  <si>
+    <t>JT9002630635983</t>
+  </si>
+  <si>
+    <t>JT5513870972023</t>
+  </si>
+  <si>
+    <t>JT5514113897521</t>
+  </si>
+  <si>
+    <t>YT8893927297359</t>
+  </si>
+  <si>
+    <t>YT0701511065027</t>
+  </si>
+  <si>
+    <t>YT0701417973666</t>
+  </si>
+  <si>
+    <t>YT8893603345556</t>
+  </si>
+  <si>
+    <t>YT8893753537049</t>
+  </si>
+  <si>
+    <t>JT5514251343504</t>
+  </si>
+  <si>
+    <t>JT5515103455832</t>
+  </si>
+  <si>
+    <t>JT5514366380148</t>
+  </si>
+  <si>
+    <t>JT5513864452084</t>
+  </si>
+  <si>
+    <t>13.08.26</t>
   </si>
 </sst>
 </file>
@@ -384,16 +189,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -915,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
@@ -935,493 +734,483 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2">
+        <v>8200443693521</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>9818636146318</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>465580401727419</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>777435018724159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>465583330213192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>777435343890019</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>9818645079994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>9818590707776</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>79130375055265</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>9818591328486</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>777435164554151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>777434990462240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>465578424722236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>9818642414455</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>777434351560656</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>79130274448824</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>465578311147993</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>9818644951424</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>465580826023570</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>9818631639538</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>9840030374709</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>9818600175463</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>777434506666952</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>777435351332185</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>777435035694786</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>79130143110425</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>9840004280016</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>79130322188117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>777434456545990</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>9818593453144</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>9818654424503</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>9818643788381</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>777434280772084</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>9840006010501</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>9818629818882</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>465578051542107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>9818627138675</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>777435025666846</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>465570902374412</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>777434390270214</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>465579140601896</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>777434297610954</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>777434295567852</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>773435854529975</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>465579400399077</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>465571656078034</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>465571656078034</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>465579119943647</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>465582471070146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>777434233604218</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>777434884882435</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>777434299301964</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>313082691804394</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>777434946844488</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>777434884881930</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>435307032391454</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>79130494504955</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>465582327633731</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>79129480026947</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>79129956787218</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>79130449704992</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>79130656900441</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>79130533639222</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>79130458508416</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>9818636146318</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B97" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B99" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/china.xlsx
+++ b/china.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>Track</t>
   </si>
@@ -115,6 +115,99 @@
   </si>
   <si>
     <t>13.08.26</t>
+  </si>
+  <si>
+    <t>YT8893328872674</t>
+  </si>
+  <si>
+    <t>YT8893573902391</t>
+  </si>
+  <si>
+    <t>JT5514806504489</t>
+  </si>
+  <si>
+    <t>YT8893568735430</t>
+  </si>
+  <si>
+    <t>YT8893553629908</t>
+  </si>
+  <si>
+    <t>JT5515013775852</t>
+  </si>
+  <si>
+    <t>JT5515325105649</t>
+  </si>
+  <si>
+    <t>YT8893529184215</t>
+  </si>
+  <si>
+    <t>YT0702550991045</t>
+  </si>
+  <si>
+    <t>YT8893735361495</t>
+  </si>
+  <si>
+    <t>YT8893459036910</t>
+  </si>
+  <si>
+    <t>YT8893707568215</t>
+  </si>
+  <si>
+    <t>YT0702471925297</t>
+  </si>
+  <si>
+    <t>YT8893437760297</t>
+  </si>
+  <si>
+    <t>YT0702581563916</t>
+  </si>
+  <si>
+    <t>YT8893659852668</t>
+  </si>
+  <si>
+    <t>YT8893609315751</t>
+  </si>
+  <si>
+    <t>JT5514154028743</t>
+  </si>
+  <si>
+    <t>JT5515382703484</t>
+  </si>
+  <si>
+    <t>JT5514318815720</t>
+  </si>
+  <si>
+    <t>JT5514331870580</t>
+  </si>
+  <si>
+    <t>YT8893606621372</t>
+  </si>
+  <si>
+    <t>YT8893663683449</t>
+  </si>
+  <si>
+    <t>JT5514772403108</t>
+  </si>
+  <si>
+    <t>JT5514273420118</t>
+  </si>
+  <si>
+    <t>JT5515333619926</t>
+  </si>
+  <si>
+    <t>JT5514387160969</t>
+  </si>
+  <si>
+    <t>JT5514191133250</t>
+  </si>
+  <si>
+    <t>JT5514222047724</t>
+  </si>
+  <si>
+    <t>JT5514369771159</t>
+  </si>
+  <si>
+    <t>15.08.26</t>
   </si>
 </sst>
 </file>
@@ -714,15 +807,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D97"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D175"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" customWidth="1"/>
-    <col min="4" max="4" width="23.109375" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -733,484 +826,874 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>8200443693521</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>9818636146318</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>465580401727419</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>777435018724159</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>465583330213192</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>777435343890019</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>9818645079994</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>9818590707776</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>79130375055265</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>9818591328486</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>777435164554151</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>777434990462240</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>465578424722236</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>9818642414455</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>777434351560656</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>79130274448824</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>465578311147993</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>9818644951424</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>465580826023570</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>9818631639538</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>9840030374709</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>9818600175463</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>777434506666952</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>777435351332185</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>777435035694786</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>79130143110425</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>9840004280016</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>79130322188117</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>777434456545990</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>9818593453144</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>9818654424503</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>9818643788381</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>777434280772084</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>9840006010501</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>9818629818882</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>465578051542107</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>9818627138675</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>777435025666846</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>465570902374412</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>777434390270214</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>465579140601896</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>777434297610954</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>777434295567852</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>773435854529975</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>465579400399077</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>465571656078034</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>465571656078034</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>465579119943647</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>465582471070146</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>777434233604218</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>777434884882435</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>777434299301964</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>313082691804394</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>777434946844488</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>777434884881930</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>435307032391454</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>79130494504955</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>465582327633731</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>79129480026947</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>79129956787218</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>79130449704992</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>79130656900441</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>79130533639222</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>79130458508416</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>9818636146318</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>777435353876275</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>465580835799057</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>9818617018947</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>465578912722442</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>777435252663232</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>9818601514151</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>9818610359642</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>9818613092601</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>465582936597633</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>777436034549323</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>777435457067840</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>777435490412564</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>773436555560374</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>777435391763316</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>79130364270671</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>465581814789127</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>777435921603737</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>465588881652713</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>465588489250632</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>465580490864093</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>777435424905540</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>465581312531999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>777435223838178</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>777435877234853</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>773436470982899</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>465582279909107</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>777435252517930</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>9818688573287</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>9818617576374</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>79130707695017</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>9818654269552</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>777435226494580</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>9818644786454</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>79131026087503</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>79130421641222</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>465582217151986</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>9818655262041</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>79130706635294</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>79131225335597</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>9818650608648</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>79130611869731</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>8216193224121</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>79130603998795</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>79130567443930</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>79130479184776</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>79025184696373</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>8201623748621</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B175" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1222,7 +1705,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1231,7 +1714,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
